--- a/Result/checksun_type/商業應用.xlsx
+++ b/Result/checksun_type/商業應用.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>48.32</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>49.46</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>55.04</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>49.46</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>55.04</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>289324693.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>359053739.8</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>359053739.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>779219302.6</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>1233289107.3</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>1233289107.3</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-90860825.19125909</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>289324693</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>289324693.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>48.31</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>49.57</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>55.39</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>49.57</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>55.39</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>298587633.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>427404646.6</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>427404646.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>788465115.2</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>1336844077.5</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>1336844077.5</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-80434512.81531477</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>298587633</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>298587633.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>48.41</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>49.77</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>55.78</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>49.77</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>55.78</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>302147334.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>549695262.2</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>549695262.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>789932410.0</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>1388106125.2</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>1388106125.2</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-63659577.53484738</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>302147334</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>302147334.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>49.14</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>56.17</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>50</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>56.17</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>429086972.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>664802561.8</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>664802561.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>805598718.5</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>1482928219.1</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>1482928219.1</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-37803224.47222078</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>429086972</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>429086972.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>49.73999999999999</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>50.18</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>56.62</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>50.18</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>56.62</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>476122067.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>751503060.6</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>751503060.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>853426202.9</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>1565117969.24</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>1565117969.24</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-13116137.5801748</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>476122067</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>476122067.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>50.16</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>50.38</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>57.1</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>50.38</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>57.1</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>631079227.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>1199384865.4</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>1199384865.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>852262787.8</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>1647059956.98</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>1647059956.98</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>17580088.42918277</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>631079227</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>631079227.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>50.69</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>50.56</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>57.56</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>50.56</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>57.56</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>910040711.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>1149525583.8</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>1149525583.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>840320195.5</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>1776903570.96</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>1776903570.96</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>44201426.71293712</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>910040711</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>910040711.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>50.32</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>50.72</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>58.07</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>50.72</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>58.07</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>877683832.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>1030169557.8</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>1030169557.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>806899222.5</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>1957468999.34</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>1957468999.34</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>50764557.16426682</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>877683832</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>877683832.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>49.52</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>50.73</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>58.46</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>50.73</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>58.46</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>862589466.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>946394875.2</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>946394875.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>771003853.8</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>2163437979.1</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>2163437979.1</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>61794246.37458563</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>862589466</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>862589466.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>48.86</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>50.84</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>50.84</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>58.9</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>2715531091.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>955349345.2</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>955349345.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>721647627.7</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>2402549153.18</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>2402549153.18</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>76961261.37594843</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>2715531091</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>2715531091.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>48.84</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>50.98</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>59.29</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>50.98</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>59.29</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>381782819.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>505140710.2</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>505140710.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>501963719.2</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>2548936714.28</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>2548936714.28</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-102649650.6355312</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>381782819</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>381782819.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>147.4</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>152.38</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>162.89</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>152.38</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>162.89</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>24025977.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>22069443.8</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>22069443.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>38876521.7</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>48446079.94</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>48446079.94</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-3611021.530052178</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>24025977</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>24025977.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>146.4</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>153.18</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>163.27</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>153.18</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>163.27</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>17661917.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>26724891.6</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>26724891.6</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>39351781.0</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>49034184.34</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>49034184.34</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-3352383.651453033</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>17661917</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>17661917.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>145.8</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>154.0</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>163.71</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>154</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>163.71</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>20757282.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>37721431.2</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>37721431.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>42011119.6</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>49452058.04</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>49452058.04</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-2181309.408759505</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>20757282</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>20757282.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>145.7</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>154.85</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>164.12</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>154.85</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>164.12</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>22500479.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>45867104.6</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>45867104.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>47656458.6</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>49685855.8</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>49685855.8</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-762088.5474559143</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>22500479</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>22500479.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>146.7</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>155.8</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>164.59</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>155.8</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>164.59</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>25401564.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>52979779.0</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>52979779</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>47185132.3</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>49884575.96</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>49884575.96</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>1105816.166815504</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>25401564</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>25401564.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>147.6</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>156.57</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>165.04</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>156.57</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>165.04</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>47303216.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>55683599.6</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>55683599.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>48088004.5</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>49740798.42</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>49740798.42</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>3423927.502674118</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>47303216</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>47303216.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>149.5</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>157.6</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>165.54</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>157.6</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>165.54</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>72644615.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>51978670.4</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>51978670.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>45211777.8</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>49699632.24</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>49699632.24</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>4266626.428805202</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>72644615</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>72644615.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>150.9</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>158.6</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>166.02</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>158.6</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>166.02</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>61485649.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>46300808.0</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>46300808</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>42600143.9</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>48671879.8</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>48671879.8</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>2602952.629392281</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>61485649</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>61485649.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>152.1</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>159.52</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>166.41</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>159.52</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>166.41</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>58063851.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>49445812.6</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>49445812.6</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>38730712.9</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>48573325.1</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>48573325.1</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>1328916.679181233</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>58063851</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>58063851.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>153.4</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>160.38</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>166.8</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>160.38</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>166.8</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>38920667.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>41390485.6</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>41390485.6</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>35887625.4</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>48642894.44</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>48642894.44</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-171974.7739481628</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>38920667</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>38920667.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>154.5</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>161.35</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>167.23</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>161.35</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>167.23</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>28778570.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>40492409.4</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>40492409.4</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>38147945.0</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>49369892.62</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>49369892.62</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-258908.0364919975</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>28778570</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>28778570.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>51.86</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>54.78</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>58.02</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>54.78</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>58.02</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>16370637.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>14968564.6</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>14968564.6</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>25991927.5</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>55328963.9</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>55328963.9</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-3761738.343921479</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>16370637</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>16370637.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>51.73999999999999</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>55.01</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>58.25</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>55.01</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>58.25</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>14210191.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>15743790.2</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>15743790.2</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>25956465.7</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>65312254.98</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>65312254.98</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-3880161.860334959</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>14210191</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>14210191.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>51.73999999999999</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>55.27</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>58.46</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>55.27</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>58.46</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>15825778.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>21316600.4</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>21316600.4</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>25649746.9</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>67714501.66</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>67714501.66</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-3679284.745913677</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>15825778</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>15825778.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>52.14</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>55.59</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>58.66</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>55.59</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>58.66</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>17027345.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>22754558.0</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>22754558</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>26782636.3</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>69191727.6</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>69191727.59999999</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-3434013.020100649</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>17027345</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>17027345.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>52.67999999999999</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>55.92</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>58.83</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>55.92</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>58.83</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>11408872.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>28718377.4</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>28718377.4</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>27355481.5</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>69373581.34</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>69373581.34</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-3089720.839649871</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>11408872</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>11408872.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>53.23999999999999</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>56.26</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>58.96</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>56.26</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>58.96</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>20246765.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>37015290.4</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>37015290.4</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>28888889.5</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>69945836.02</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>69945836.02</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-1885548.444732688</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>20246765</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>20246765.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>54.21999999999999</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>56.57</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>59.12</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>56.57</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>59.12</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>42074242.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>36169141.2</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>36169141.2</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>29060387.7</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>70323701.58</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>70323701.58</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-1044878.257539123</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>42074242</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>42074242.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>55.12</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>56.86</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>59.28</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>56.86</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>59.28</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>23015566.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>29982893.4</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>29982893.4</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>27325142.8</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>70871687.6</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>70871687.59999999</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-2145262.016636197</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>23015566</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>23015566.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>55.72000000000001</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>57.07</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>59.42</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>57.07</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>59.42</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>46846442.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>30810714.6</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>30810714.6</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>28427276.6</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>71965384.46</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>71965384.45999999</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-1598621.314752154</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>46846442</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>46846442.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>56.22000000000001</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>57.31</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>59.56</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>57.31</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>59.56</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>52893437.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>25992585.6</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>25992585.6</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>25254632.5</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>72823093.42</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>72823093.42</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-3313920.550819516</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>52893437</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>52893437.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>56.66</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>57.52</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>59.68</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>57.52</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>59.68</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>16016019.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>20762488.6</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>20762488.6</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>23044675.4</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>73396602.94</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>73396602.94</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-6293886.04695791</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>16016019</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>16016019.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>

--- a/Result/checksun_type/商業應用.xlsx
+++ b/Result/checksun_type/商業應用.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6477.386</t>
+          <t>4440.277</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>48.95</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-31.98</t>
+          <t>-23.09</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-27.48</t>
+          <t>-28.15</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>6477</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.52</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>65.42</t>
+          <t>64.49</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-8.97</t>
+          <t>-8.4</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>49.09</t>
+          <t>49.12</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>49.23</v>
+        <v>49.17</v>
       </c>
       <c r="AN2" t="n">
-        <v>54.08</v>
+        <v>53.68</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>56.01</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>20.72</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-121.89</t>
+          <t>-120.81</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1133097683.061966</t>
+          <t>1131949560.733997</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>319770748.0</t>
+          <t>217311791.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>283316111.4</v>
+        <v>267060943</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>416505686.8</t>
+          <t>347232794.8</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>1087982910.56</v>
+        <v>1007913686.44</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-133189575</t>
+          <t>-80171851</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-74959775.3529597</t>
+          <t>-78323679.09920117</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-95106052.24594092</t>
+          <t>-96825149.70352924</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>319770748.0</t>
+          <t>217311791.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>22.07</t>
+          <t>20.95</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>7.03</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>29.73</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>40890</t>
+          <t>40514</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>48.95</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6085.789</t>
+          <t>6477.386</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>48.95</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-40.76</t>
+          <t>-31.98</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-26.00</t>
+          <t>-27.48</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>6477</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>56.52</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>59.82</t>
+          <t>65.42</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-9.3</t>
+          <t>-8.97</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>48.83</t>
+          <t>49.09</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>49.37</v>
+        <v>49.23</v>
       </c>
       <c r="AN3" t="n">
-        <v>54.43</v>
+        <v>54.08</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>55.92</t>
+          <t>56.01</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-123.12</t>
+          <t>-121.89</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1133097683.061966</t>
+          <t>1131949560.733997</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>302011850.0</t>
+          <t>319770748.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>279791428.6</v>
+        <v>283316111.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>472296995.2</t>
+          <t>416505686.8</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>1139949931.8</v>
+        <v>1087982910.56</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-192505566</t>
+          <t>-133189575</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-71296815.91787222</t>
+          <t>-74959775.3529597</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-100231299.4048884</t>
+          <t>-95106052.24594092</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>302011850.0</t>
+          <t>319770748.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>24.56</t>
+          <t>22.07</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>7.03</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>29.73</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>40890</t>
+          <t>40514</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
+          <t>48.8</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
           <t>48.95</t>
-        </is>
-      </c>
-      <c r="CG3" t="inlineStr">
-        <is>
-          <t>49.95</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4211.204</t>
+          <t>6085.789</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-42.23</t>
+          <t>-40.76</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-27.26</t>
+          <t>-26.00</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>6477</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>39.73</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>32.88</t>
+          <t>59.82</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-9.69</t>
+          <t>-9.3</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>48.83</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>49.4</v>
+        <v>49.37</v>
       </c>
       <c r="AN4" t="n">
-        <v>54.69</v>
+        <v>54.43</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>55.82</t>
+          <t>55.92</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>16.10</t>
+          <t>22.18</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-124.40</t>
+          <t>-123.12</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1133097683.061966</t>
+          <t>1131949560.733997</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>206885633.0</t>
+          <t>302011850.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>305206453</v>
+        <v>279791428.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>528354756.8</t>
+          <t>472296995.2</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>1193416018.88</v>
+        <v>1139949931.8</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-223148303</t>
+          <t>-192505566</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-66036000.73841473</t>
+          <t>-71296815.91787222</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-102070652.7246387</t>
+          <t>-100231299.4048884</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>206885633.0</t>
+          <t>302011850.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>24.56</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>7.03</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>29.73</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>40890</t>
+          <t>40514</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>48.95</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5896.567</t>
+          <t>4211.204</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-53.92</t>
+          <t>-42.23</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,12 +2304,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>6477</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2319,58 +2319,58 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>19.63</t>
+          <t>32.88</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-10.14</t>
+          <t>-9.69</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>49.46</v>
+        <v>49.4</v>
       </c>
       <c r="AN5" t="n">
-        <v>55.04</v>
+        <v>54.69</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>55.71</t>
+          <t>55.82</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>12.90</t>
+          <t>16.10</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-125.39</t>
+          <t>-124.40</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1133097683.061966</t>
+          <t>1131949560.733997</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>289324693.0</t>
+          <t>206885633.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>359053739.8</v>
+        <v>305206453</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>779219302.6</t>
+          <t>528354756.8</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>1233289107.3</v>
+        <v>1193416018.88</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-420165562</t>
+          <t>-223148303</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-59484245.83182855</t>
+          <t>-66036000.73841473</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-90860825.19125909</t>
+          <t>-102070652.7246387</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>289324693.0</t>
+          <t>206885633.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>7.03</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>29.73</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>40890</t>
+          <t>40514</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,17 +2556,17 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6182.1</t>
+          <t>5896.567</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-45.79</t>
+          <t>-53.92</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-28.37</t>
+          <t>-27.26</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>6477</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>19.18</t>
+          <t>39.73</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>19.63</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-10.51</t>
+          <t>-10.14</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>48.31</t>
+          <t>48.32</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>49.57</v>
+        <v>49.46</v>
       </c>
       <c r="AN6" t="n">
-        <v>55.39</v>
+        <v>55.04</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>55.71</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>12.90</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-126.20</t>
+          <t>-125.39</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1133097683.061966</t>
+          <t>1131949560.733997</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>298587633.0</t>
+          <t>289324693.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>427404646.6</v>
+        <v>359053739.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>788465115.2</t>
+          <t>779219302.6</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>1336844077.5</v>
+        <v>1233289107.3</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-361060468</t>
+          <t>-420165562</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-53779413.22102299</t>
+          <t>-59484245.83182855</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-80434512.81531477</t>
+          <t>-90860825.19125909</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>298587633.0</t>
+          <t>289324693.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>20.57</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>7.03</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>29.73</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>40890</t>
+          <t>40514</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6337.117</t>
+          <t>6182.1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.35</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-30.41</t>
+          <t>-45.79</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-29.41</t>
+          <t>-28.37</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>6477</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.18</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>17.73</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-10.77</t>
+          <t>-10.51</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>48.41</t>
+          <t>48.31</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>49.77</v>
+        <v>49.57</v>
       </c>
       <c r="AN7" t="n">
-        <v>55.78</v>
+        <v>55.39</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>55.51</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>7.76</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-126.78</t>
+          <t>-126.20</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1133097683.061966</t>
+          <t>1131949560.733997</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>302147334.0</t>
+          <t>298587633.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>549695262.2</v>
+        <v>427404646.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>789932410.0</t>
+          <t>788465115.2</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>1388106125.2</v>
+        <v>1336844077.5</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-240237147</t>
+          <t>-361060468</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-48933031.4766063</t>
+          <t>-53779413.22102299</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-63659577.53484738</t>
+          <t>-80434512.81531477</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>302147334.0</t>
+          <t>298587633.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>20.57</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>7.03</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>29.73</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>40890</t>
+          <t>40514</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
+          <t>48.15</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>48.8</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
           <t>47.9</t>
         </is>
       </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>48.1</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>47.3</t>
-        </is>
-      </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.35</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8966.946</t>
+          <t>6337.117</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-17.48</t>
+          <t>-30.41</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-29.19</t>
+          <t>-29.41</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>6477</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>32.27</t>
+          <t>17.73</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
+          <t>-1.57</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
           <t>-2.73</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>-1.71</t>
-        </is>
-      </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-11.0</t>
+          <t>-10.77</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>49.14</t>
+          <t>48.41</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>50</v>
+        <v>49.77</v>
       </c>
       <c r="AN8" t="n">
-        <v>56.17</v>
+        <v>55.78</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>55.43</t>
+          <t>55.51</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>10.69</t>
+          <t>7.76</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-127.30</t>
+          <t>-126.78</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1133097683.061966</t>
+          <t>1131949560.733997</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>429086972.0</t>
+          <t>302147334.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>664802561.8</v>
+        <v>549695262.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>805598718.5</t>
+          <t>789932410.0</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>1482928219.1</v>
+        <v>1388106125.2</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-140796156</t>
+          <t>-240237147</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-46255477.6478352</t>
+          <t>-48933031.4766063</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-37803224.47222078</t>
+          <t>-63659577.53484738</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>429086972.0</t>
+          <t>302147334.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>19.20</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>7.03</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>29.73</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>40890</t>
+          <t>40514</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>47.25</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>9634.482</t>
+          <t>8966.946</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-11.94</t>
+          <t>-17.48</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-27.85</t>
+          <t>-29.19</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>6477</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>36.17</t>
+          <t>17.02</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>32.27</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-11.37</t>
+          <t>-11.0</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>49.73999999999999</t>
+          <t>49.14</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>50.18</v>
+        <v>50</v>
       </c>
       <c r="AN9" t="n">
-        <v>56.62</v>
+        <v>56.17</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>55.33</t>
+          <t>55.43</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>10.69</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-128.03</t>
+          <t>-127.30</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1133097683.061966</t>
+          <t>1131949560.733997</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>476122067.0</t>
+          <t>429086972.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>751503060.6</v>
+        <v>664802561.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>853426202.9</t>
+          <t>805598718.5</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>1565117969.24</v>
+        <v>1482928219.1</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-101923142</t>
+          <t>-140796156</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-47792250.95249236</t>
+          <t>-46255477.6478352</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-13116137.5801748</t>
+          <t>-37803224.47222078</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>476122067.0</t>
+          <t>429086972.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>19.20</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>7.03</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>29.73</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>40890</t>
+          <t>40514</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.25</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>12834.389</t>
+          <t>9634.482</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>40.73</t>
+          <t>-11.94</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-27.33</t>
+          <t>-27.85</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>6477</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>43.62</t>
+          <t>36.17</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>58.16</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-11.78</t>
+          <t>-11.37</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>50.16</t>
+          <t>49.73999999999999</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>50.38</v>
+        <v>50.18</v>
       </c>
       <c r="AN10" t="n">
-        <v>57.1</v>
+        <v>56.62</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>55.23</t>
+          <t>55.33</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>17.13</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.70</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-129.08</t>
+          <t>-128.03</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1133097683.061966</t>
+          <t>1131949560.733997</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>631079227.0</t>
+          <t>476122067.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>1199384865.4</v>
+        <v>751503060.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>852262787.8</t>
+          <t>853426202.9</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>1647059956.98</v>
+        <v>1565117969.24</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>347122077</t>
+          <t>-101923142</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-54096998.83836829</t>
+          <t>-47792250.95249236</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>17580088.42918277</t>
+          <t>-13116137.5801748</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>631079227.0</t>
+          <t>476122067.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,17 +4641,17 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>7.03</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>29.73</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>40890</t>
+          <t>40514</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-4.8</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>18405.677</t>
+          <t>12834.389</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>36.80</t>
+          <t>40.73</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-27.63</t>
+          <t>-27.33</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10.58</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>6477</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>39.36</t>
+          <t>43.62</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>70.57</t>
+          <t>58.16</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-12.16</t>
+          <t>-11.78</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>50.69</t>
+          <t>50.16</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>50.56</v>
+        <v>50.38</v>
       </c>
       <c r="AN11" t="n">
-        <v>57.56</v>
+        <v>57.1</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>55.11</t>
+          <t>55.23</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>17.13</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-130.33</t>
+          <t>-129.08</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1133097683.061966</t>
+          <t>1131949560.733997</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>910040711.0</t>
+          <t>631079227.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>1149525583.8</v>
+        <v>1199384865.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>840320195.5</t>
+          <t>852262787.8</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>1776903570.96</v>
+        <v>1647059956.98</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>309205388</t>
+          <t>347122077</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-67129196.52337757</t>
+          <t>-54096998.83836829</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>44201426.71293712</t>
+          <t>17580088.42918277</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>910040711.0</t>
+          <t>631079227.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>21.82</t>
+          <t>22.32</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>7.03</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>29.73</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>40890</t>
+          <t>40514</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-4.8</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>16934.062</t>
+          <t>18405.677</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-4.8</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>36.80</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-24.00</t>
+          <t>-27.63</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>10.58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,63 +5314,63 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>6477</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>91.49</t>
+          <t>39.36</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>70.57</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-12.67</t>
+          <t>-12.16</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>50.32</t>
+          <t>50.69</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>50.72</v>
+        <v>50.56</v>
       </c>
       <c r="AN12" t="n">
-        <v>58.07</v>
+        <v>57.56</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>55.11</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>22.67</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -5380,7 +5380,7 @@
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-131.76</t>
+          <t>-130.33</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1133097683.061966</t>
+          <t>1131949560.733997</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>877683832.0</t>
+          <t>910040711.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>1030169557.8</v>
+        <v>1149525583.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>806899222.5</t>
+          <t>840320195.5</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>1957468999.34</v>
+        <v>1776903570.96</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>223270335</t>
+          <t>309205388</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-87371128.02088934</t>
+          <t>-67129196.52337757</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>50764557.16426682</t>
+          <t>44201426.71293712</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>877683832.0</t>
+          <t>910040711.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>27.93</t>
+          <t>21.82</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>7.03</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>29.73</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>40890</t>
+          <t>40514</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5571,17 +5571,17 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>47.95</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>217.695</t>
+          <t>221.182</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5648,7 +5648,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-29.52</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-10.26</t>
+          <t>-10.56</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,32 +5744,32 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>221</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.75</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>97.92</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -5779,38 +5779,38 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>150.6</t>
+          <t>151.5</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>151.02</v>
+        <v>150.72</v>
       </c>
       <c r="AN13" t="n">
-        <v>161.92</v>
+        <v>161.6</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>166.28</t>
+          <t>166.06</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-166.59</t>
+          <t>-161.99</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>86284468.51923077</t>
+          <t>86233562.9679943</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>33440159.0</t>
+          <t>33665244.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>20524714.4</v>
+        <v>23725379.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>29123072.8</t>
+          <t>25225135.7</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>47828163.38</v>
+        <v>47594496.58</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-8598358</t>
+          <t>-1499755</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-2269714.667708008</t>
+          <t>-2331202.960361985</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-3642407.501406003</t>
+          <t>-2669388.569958854</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>33440159.0</t>
+          <t>33665244.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,22 +5931,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>19.34</t>
+          <t>19.28</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>16273</t>
+          <t>16220</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6001,17 +6001,17 @@
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>154.5</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
+          <t>151.0</t>
+        </is>
+      </c>
+      <c r="CG13" t="inlineStr">
+        <is>
           <t>152.5</t>
-        </is>
-      </c>
-      <c r="CG13" t="inlineStr">
-        <is>
-          <t>153.0</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>113.756</t>
+          <t>217.695</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-43.66</t>
+          <t>-29.52</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-10.56</t>
+          <t>-10.26</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,12 +6174,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>221</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6189,58 +6189,58 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>94.44</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-6.63</t>
+          <t>-6.73</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>149.6</t>
+          <t>150.6</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>151.48</v>
+        <v>151.02</v>
       </c>
       <c r="AN14" t="n">
-        <v>162.23</v>
+        <v>161.92</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>166.46</t>
+          <t>166.28</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>18.56</t>
+          <t>25.26</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-170.79</t>
+          <t>-166.59</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>86284468.51923077</t>
+          <t>86233562.9679943</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>17265960.0</t>
+          <t>33440159.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>17988139</v>
+        <v>20524714.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>31927621.8</t>
+          <t>29123072.8</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>47822091</v>
+        <v>47828163.38</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-13939482</t>
+          <t>-8598358</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-2020134.152490191</t>
+          <t>-2269714.667708008</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-4878232.314137429</t>
+          <t>-3642407.501406003</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>17265960.0</t>
+          <t>33440159.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>19.34</t>
+          <t>19.28</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>16273</t>
+          <t>16220</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
+          <t>154.5</t>
+        </is>
+      </c>
+      <c r="CF14" t="inlineStr">
+        <is>
           <t>152.5</t>
         </is>
       </c>
-      <c r="CF14" t="inlineStr">
-        <is>
-          <t>151.0</t>
-        </is>
-      </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>68.169</t>
+          <t>113.756</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,7 +6498,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-47.14</t>
+          <t>-43.66</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-11.73</t>
+          <t>-10.56</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,12 +6604,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>221</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6619,58 +6619,58 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>78.89</t>
+          <t>94.44</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-6.57</t>
+          <t>-6.63</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>148.1</t>
+          <t>149.6</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>151.85</v>
+        <v>151.48</v>
       </c>
       <c r="AN15" t="n">
-        <v>162.53</v>
+        <v>162.23</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>166.62</t>
+          <t>166.46</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>10.76</t>
+          <t>18.56</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-4.37</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-4.89</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-174.08</t>
+          <t>-170.79</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>86284468.51923077</t>
+          <t>86233562.9679943</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>10229559.0</t>
+          <t>17265960.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>19035042.8</v>
+        <v>17988139</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>36007410.9</t>
+          <t>31927621.8</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>48032153.96</v>
+        <v>47822091</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-16972368</t>
+          <t>-13939482</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-1500479.941281602</t>
+          <t>-2020134.152490191</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-4736523.85682027</t>
+          <t>-4878232.314137429</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>10229559.0</t>
+          <t>17265960.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6801,12 +6801,12 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>19.34</t>
+          <t>19.28</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>16273</t>
+          <t>16220</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
+          <t>152.5</t>
+        </is>
+      </c>
+      <c r="CF15" t="inlineStr">
+        <is>
           <t>151.0</t>
         </is>
       </c>
-      <c r="CF15" t="inlineStr">
-        <is>
-          <t>149.0</t>
-        </is>
-      </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,127 +6903,127 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>1.01</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>68.169</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>150.5</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>-47.14</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2025-09-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2025-08-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2025-08-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>171.5</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>170.5</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>167.5</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>173.5</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>-11.73</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>-1.15</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
           <t>0.67</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>160.971</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>149.0</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>2.61</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>-43.23</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>2025-09-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>2025-08-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>2025-08-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>171.5</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>170.5</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>167.5</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>173.5</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>-12.61</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>-1.15</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>3.02</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>-0.33</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>221</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>59.59</t>
+          <t>78.89</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-6.46</t>
+          <t>-6.57</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>147.4</t>
+          <t>148.1</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>152.38</v>
+        <v>151.85</v>
       </c>
       <c r="AN16" t="n">
-        <v>162.89</v>
+        <v>162.53</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>166.78</t>
+          <t>166.62</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>10.76</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-4.81</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-4.89</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-176.07</t>
+          <t>-174.08</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>86284468.51923077</t>
+          <t>86233562.9679943</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>24025977.0</t>
+          <t>10229559.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>22069443.8</v>
+        <v>19035042.8</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>38876521.7</t>
+          <t>36007410.9</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>48446079.94</v>
+        <v>48032153.96</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-16807077</t>
+          <t>-16972368</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-912108.3202745712</t>
+          <t>-1500479.941281602</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-3611021.530052178</t>
+          <t>-4736523.85682027</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>24025977.0</t>
+          <t>10229559.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-6.88</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>19.34</t>
+          <t>19.28</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>16273</t>
+          <t>16220</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7323,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7333,42 +7333,42 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>0.67</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>160.971</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>118.956</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>148.0</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>3.27</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-32.09</t>
+          <t>-43.23</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-13.20</t>
+          <t>-12.61</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,22 +7464,22 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>221</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>53.33</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>35.32</t>
+          <t>59.59</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
@@ -7489,48 +7489,48 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>-6.46</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>146.4</t>
+          <t>147.4</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>153.18</v>
+        <v>152.38</v>
       </c>
       <c r="AN17" t="n">
-        <v>163.27</v>
+        <v>162.89</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>166.96</t>
+          <t>166.78</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-5.16</t>
+          <t>-4.81</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-5.08</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-176.87</t>
+          <t>-176.07</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>86284468.51923077</t>
+          <t>86233562.9679943</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>17661917.0</t>
+          <t>24025977.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>26724891.6</v>
+        <v>22069443.8</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>39351781.0</t>
+          <t>38876521.7</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>49034184.34</v>
+        <v>48446079.94</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-12626889</t>
+          <t>-16807077</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-421396.8275877337</t>
+          <t>-912108.3202745712</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-3352383.651453033</t>
+          <t>-3611021.530052178</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>17661917.0</t>
+          <t>24025977.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-7.50</t>
+          <t>-6.88</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7661,12 +7661,12 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>4.80</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>19.34</t>
+          <t>19.28</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>16273</t>
+          <t>16220</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
+          <t>148.5</t>
+        </is>
+      </c>
+      <c r="CE17" t="inlineStr">
+        <is>
           <t>150.0</t>
         </is>
       </c>
-      <c r="CE17" t="inlineStr">
-        <is>
-          <t>150.0</t>
-        </is>
-      </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>141.444</t>
+          <t>118.956</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -7798,7 +7798,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-10.21</t>
+          <t>-32.09</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>221</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>53.33</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>28.07</t>
+          <t>35.32</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-5.32</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-5.93</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>145.8</t>
+          <t>146.4</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>154</v>
+        <v>153.18</v>
       </c>
       <c r="AN18" t="n">
-        <v>163.71</v>
+        <v>163.27</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>167.13</t>
+          <t>166.96</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-7.24</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-5.42</t>
+          <t>-5.16</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-5.06</t>
+          <t>-5.08</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-176.57</t>
+          <t>-176.87</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>86284468.51923077</t>
+          <t>86233562.9679943</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>20757282.0</t>
+          <t>17661917.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>37721431.2</v>
+        <v>26724891.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>42011119.6</t>
+          <t>39351781.0</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>49452058.04</v>
+        <v>49034184.34</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-4289688</t>
+          <t>-12626889</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>111509.8676605026</t>
+          <t>-421396.8275877337</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-2181309.408759505</t>
+          <t>-3352383.651453033</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>20757282.0</t>
+          <t>17661917.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>19.34</t>
+          <t>19.28</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>16273</t>
+          <t>16220</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,17 +8146,17 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>154.647</t>
+          <t>141.444</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,7 +8218,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>5.23</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-10.21</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-14.96</t>
+          <t>-13.20</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>221</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>42.11</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>14.04</t>
+          <t>28.07</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-5.91</t>
+          <t>-5.32</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-5.65</t>
+          <t>-5.93</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>145.7</t>
+          <t>145.8</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>154.85</v>
+        <v>154</v>
       </c>
       <c r="AN19" t="n">
-        <v>164.12</v>
+        <v>163.71</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>167.29</t>
+          <t>167.13</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-14.44</t>
+          <t>-7.24</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-5.68</t>
+          <t>-5.42</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-4.97</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-175.18</t>
+          <t>-176.57</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>86284468.51923077</t>
+          <t>86233562.9679943</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>22500479.0</t>
+          <t>20757282.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>45867104.6</v>
+        <v>37721431.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>47656458.6</t>
+          <t>42011119.6</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>49685855.8</v>
+        <v>49452058.04</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-1789354</t>
+          <t>-4289688</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>528386.0997368675</t>
+          <t>111509.8676605026</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-762088.5474559143</t>
+          <t>-2181309.408759505</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>22500479.0</t>
+          <t>20757282.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-9.38</t>
+          <t>-7.50</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8521,12 +8521,12 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>4.70</t>
+          <t>4.80</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>19.34</t>
+          <t>19.28</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>16273</t>
+          <t>16220</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8581,17 +8581,17 @@
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>173.621</t>
+          <t>154.647</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>12.28</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-13.78</t>
+          <t>-14.96</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,73 +8754,73 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>221</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>31.58</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>14.04</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-5.84</t>
+          <t>-5.91</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-5.34</t>
+          <t>-5.65</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>146.7</t>
+          <t>145.7</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>155.8</v>
+        <v>154.85</v>
       </c>
       <c r="AN20" t="n">
-        <v>164.59</v>
+        <v>164.12</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>167.49</t>
+          <t>167.29</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-17.54</t>
+          <t>-14.44</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-5.63</t>
+          <t>-5.68</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>-4.97</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-172.47</t>
+          <t>-175.18</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>86284468.51923077</t>
+          <t>86233562.9679943</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>25401564.0</t>
+          <t>22500479.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>52979779</v>
+        <v>45867104.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>47185132.3</t>
+          <t>47656458.6</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>49884575.96</v>
+        <v>49685855.8</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>5794646</t>
+          <t>-1789354</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>763017.8537719188</t>
+          <t>528386.0997368675</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>1105816.166815504</t>
+          <t>-762088.5474559143</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>25401564.0</t>
+          <t>22500479.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-8.12</t>
+          <t>-9.38</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,22 +8941,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>4.70</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>19.34</t>
+          <t>19.28</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>16273</t>
+          <t>16220</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>328.22</t>
+          <t>173.621</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,7 +9078,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -9088,7 +9088,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>15.80</t>
+          <t>12.28</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-15.54</t>
+          <t>-13.78</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,73 +9184,73 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>221</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>31.58</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-5.73</t>
+          <t>-5.84</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-5.13</t>
+          <t>-5.34</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>147.6</t>
+          <t>146.7</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>156.57</v>
+        <v>155.8</v>
       </c>
       <c r="AN21" t="n">
-        <v>165.04</v>
+        <v>164.59</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>167.66</t>
+          <t>167.49</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-24.00</t>
+          <t>-17.54</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-5.68</t>
+          <t>-5.63</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-4.79</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-169.29</t>
+          <t>-172.47</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>86284468.51923077</t>
+          <t>86233562.9679943</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>47303216.0</t>
+          <t>25401564.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>55683599.6</v>
+        <v>52979779</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>48088004.5</t>
+          <t>47185132.3</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>49740798.42</v>
+        <v>49884575.96</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>7595595</t>
+          <t>5794646</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>700690.8877639942</t>
+          <t>763017.8537719188</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>3423927.502674118</t>
+          <t>1105816.166815504</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>47303216.0</t>
+          <t>25401564.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-10.00</t>
+          <t>-8.12</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,22 +9371,22 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>19.34</t>
+          <t>19.28</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>16273</t>
+          <t>16220</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>499.35</t>
+          <t>328.22</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,7 +9508,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>5.23</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -9518,7 +9518,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>15.80</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-14.96</t>
+          <t>-15.54</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,12 +9614,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>221</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9634,53 +9634,53 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-5.73</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-4.8</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>147.6</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>157.6</v>
+        <v>156.57</v>
       </c>
       <c r="AN22" t="n">
-        <v>165.54</v>
+        <v>165.04</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>167.86</t>
+          <t>167.66</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-24.35</t>
+          <t>-24.00</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-5.35</t>
+          <t>-5.68</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-4.30</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-165.13</t>
+          <t>-169.29</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>86284468.51923077</t>
+          <t>86233562.9679943</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>72644615.0</t>
+          <t>47303216.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>51978670.4</v>
+        <v>55683599.6</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>45211777.8</t>
+          <t>48088004.5</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>49699632.24</v>
+        <v>49740798.42</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>6766892</t>
+          <t>7595595</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>205556.9577803353</t>
+          <t>700690.8877639942</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>4266626.428805202</t>
+          <t>3423927.502674118</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>72644615.0</t>
+          <t>47303216.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-9.38</t>
+          <t>-10.00</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>4.70</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>19.34</t>
+          <t>19.28</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>16273</t>
+          <t>16220</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
+          <t>143.0</t>
+        </is>
+      </c>
+      <c r="CG22" t="inlineStr">
+        <is>
           <t>144.0</t>
-        </is>
-      </c>
-      <c r="CG22" t="inlineStr">
-        <is>
-          <t>145.0</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>414.564</t>
+          <t>499.35</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,7 +9938,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>8.69</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-13.49</t>
+          <t>-14.96</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,12 +10044,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>221</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10064,53 +10064,53 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-4.8</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>150.9</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>158.6</v>
+        <v>157.6</v>
       </c>
       <c r="AN23" t="n">
-        <v>166.02</v>
+        <v>165.54</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>168.07</t>
+          <t>167.86</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-22.73</t>
+          <t>-24.35</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-5.35</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-4.30</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-161.17</t>
+          <t>-165.13</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>86284468.51923077</t>
+          <t>86233562.9679943</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>61485649.0</t>
+          <t>72644615.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>46300808</v>
+        <v>51978670.4</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>42600143.9</t>
+          <t>45211777.8</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>48671879.8</v>
+        <v>49699632.24</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>3700664</t>
+          <t>6766892</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-532819.3096787315</t>
+          <t>205556.9577803353</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>2602952.629392281</t>
+          <t>4266626.428805202</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>61485649.0</t>
+          <t>72644615.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-7.81</t>
+          <t>-9.38</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>4.78</t>
+          <t>4.70</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>19.34</t>
+          <t>19.28</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>16273</t>
+          <t>16220</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -10343,12 +10343,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>270.323</t>
+          <t>219.546</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-21.51</t>
+          <t>-8.63</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -10453,17 +10453,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -10474,12 +10474,12 @@
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
@@ -10489,58 +10489,58 @@
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>81.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>-5.88</t>
+          <t>-6.01</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.44</t>
         </is>
       </c>
       <c r="AM24" t="n">
-        <v>54.05</v>
+        <v>53.82</v>
       </c>
       <c r="AN24" t="n">
-        <v>57.43</v>
+        <v>57.26</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>58.53</t>
+          <t>58.43</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>8.31</t>
         </is>
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
@@ -10550,7 +10550,7 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>-122.55</t>
+          <t>-122.09</t>
         </is>
       </c>
       <c r="AU24" t="inlineStr">
@@ -10560,43 +10560,43 @@
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>331265030.4933921</t>
+          <t>330804763.1502933</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>14277948.0</t>
+          <t>11575135.0</t>
         </is>
       </c>
       <c r="AX24" t="n">
-        <v>13770572.6</v>
+        <v>13243561.4</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>17543586.5</t>
+          <t>14493675.8</t>
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>40909066.6</v>
+        <v>39880117.8</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>-3773013</t>
+          <t>-1250114</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>-3762204.121556715</t>
+          <t>-3735190.270685619</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>-3660695.180078171</t>
+          <t>-3586614.090894589</t>
         </is>
       </c>
       <c r="BD24" t="inlineStr">
         <is>
-          <t>14277948.0</t>
+          <t>11575135.0</t>
         </is>
       </c>
       <c r="BE24" t="inlineStr">
@@ -10661,7 +10661,7 @@
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
@@ -10701,7 +10701,7 @@
       </c>
       <c r="BY24" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ24" t="inlineStr">
@@ -10726,12 +10726,12 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CF24" t="inlineStr">
@@ -10763,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -10773,12 +10773,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>225.533</t>
+          <t>270.323</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -10798,17 +10798,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-23.55</t>
+          <t>-21.51</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -10873,7 +10873,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>-14.63</t>
+          <t>-14.47</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -10883,17 +10883,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -10904,12 +10904,12 @@
       <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
@@ -10919,58 +10919,58 @@
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>60.68</t>
+          <t>81.67</t>
         </is>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>-5.73</t>
+          <t>-5.88</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>52.04</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="AM25" t="n">
-        <v>54.32</v>
+        <v>54.05</v>
       </c>
       <c r="AN25" t="n">
-        <v>57.62</v>
+        <v>57.43</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>58.63</t>
+          <t>58.53</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
@@ -10980,7 +10980,7 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>-122.79</t>
+          <t>-122.55</t>
         </is>
       </c>
       <c r="AU25" t="inlineStr">
@@ -10990,43 +10990,43 @@
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>331265030.4933921</t>
+          <t>330804763.1502933</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>11807501.0</t>
+          <t>14277948.0</t>
         </is>
       </c>
       <c r="AX25" t="n">
-        <v>14080138.6</v>
+        <v>13770572.6</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>18417348.3</t>
+          <t>17543586.5</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>42382898.78</v>
+        <v>40909066.6</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>-4337209</t>
+          <t>-3773013</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>-3780660.292734632</t>
+          <t>-3762204.121556715</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>-3925373.301051926</t>
+          <t>-3660695.180078171</t>
         </is>
       </c>
       <c r="BD25" t="inlineStr">
         <is>
-          <t>11807501.0</t>
+          <t>14277948.0</t>
         </is>
       </c>
       <c r="BE25" t="inlineStr">
@@ -11046,7 +11046,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>-10.10</t>
+          <t>-9.93</t>
         </is>
       </c>
       <c r="BI25" t="inlineStr">
@@ -11091,7 +11091,7 @@
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
@@ -11131,7 +11131,7 @@
       </c>
       <c r="BY25" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ25" t="inlineStr">
@@ -11156,22 +11156,22 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -11203,12 +11203,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>232.681</t>
+          <t>225.533</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -11218,7 +11218,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -11228,17 +11228,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-31.01</t>
+          <t>-23.55</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -11303,7 +11303,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>-15.12</t>
+          <t>-14.63</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -11313,7 +11313,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
@@ -11323,7 +11323,7 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -11334,68 +11334,68 @@
       <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>32.35</t>
+          <t>60.68</t>
         </is>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>-5.06</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-5.73</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>52.04</t>
         </is>
       </c>
       <c r="AM26" t="n">
-        <v>54.56</v>
+        <v>54.32</v>
       </c>
       <c r="AN26" t="n">
-        <v>57.82</v>
+        <v>57.62</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>58.72</t>
+          <t>58.63</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>-6.38</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>-122.75</t>
+          <t>-122.79</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
@@ -11420,43 +11420,43 @@
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>331265030.4933921</t>
+          <t>330804763.1502933</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>12186586.0</t>
+          <t>11807501.0</t>
         </is>
       </c>
       <c r="AX26" t="n">
-        <v>15124107.4</v>
+        <v>14080138.6</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>21921242.4</t>
+          <t>18417348.3</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>45541967.12</v>
+        <v>42382898.78</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>-6797134</t>
+          <t>-4337209</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>-3754348.836676942</t>
+          <t>-3780660.292734632</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>-3898602.248834006</t>
+          <t>-3925373.301051926</t>
         </is>
       </c>
       <c r="BD26" t="inlineStr">
         <is>
-          <t>12186586.0</t>
+          <t>11807501.0</t>
         </is>
       </c>
       <c r="BE26" t="inlineStr">
@@ -11476,7 +11476,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>-10.62</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="BI26" t="inlineStr">
@@ -11521,7 +11521,7 @@
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
@@ -11531,7 +11531,7 @@
       </c>
       <c r="BS26" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT26" t="inlineStr">
@@ -11561,7 +11561,7 @@
       </c>
       <c r="BY26" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ26" t="inlineStr">
@@ -11586,22 +11586,22 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CF26" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -11633,12 +11633,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>312.769</t>
+          <t>232.681</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -11648,7 +11648,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -11658,17 +11658,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-42.41</t>
+          <t>-31.01</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -11733,7 +11733,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>-14.96</t>
+          <t>-15.12</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -11743,17 +11743,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -11764,73 +11764,73 @@
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>32.35</t>
         </is>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>-5.59</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>51.86</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="AM27" t="n">
-        <v>54.78</v>
+        <v>54.56</v>
       </c>
       <c r="AN27" t="n">
-        <v>58.02</v>
+        <v>57.82</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>58.78</t>
+          <t>58.72</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>-11.93</t>
+          <t>-6.38</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
@@ -11840,7 +11840,7 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>-122.39</t>
+          <t>-122.75</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
@@ -11850,43 +11850,43 @@
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>331265030.4933921</t>
+          <t>330804763.1502933</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>16370637.0</t>
+          <t>12186586.0</t>
         </is>
       </c>
       <c r="AX27" t="n">
-        <v>14968564.6</v>
+        <v>15124107.4</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>25991927.5</t>
+          <t>21921242.4</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>55328963.9</v>
+        <v>45541967.12</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>-11023362</t>
+          <t>-6797134</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>-3728120.943557476</t>
+          <t>-3754348.836676942</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>-3761738.343921479</t>
+          <t>-3898602.248834006</t>
         </is>
       </c>
       <c r="BD27" t="inlineStr">
         <is>
-          <t>16370637.0</t>
+          <t>12186586.0</t>
         </is>
       </c>
       <c r="BE27" t="inlineStr">
@@ -11906,7 +11906,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>-10.45</t>
+          <t>-10.62</t>
         </is>
       </c>
       <c r="BI27" t="inlineStr">
@@ -11951,7 +11951,7 @@
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
@@ -11961,7 +11961,7 @@
       </c>
       <c r="BS27" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BT27" t="inlineStr">
@@ -11991,7 +11991,7 @@
       </c>
       <c r="BY27" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ27" t="inlineStr">
@@ -12016,22 +12016,22 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
+          <t>53.2</t>
+        </is>
+      </c>
+      <c r="CE27" t="inlineStr">
+        <is>
+          <t>53.2</t>
+        </is>
+      </c>
+      <c r="CF27" t="inlineStr">
+        <is>
           <t>52.1</t>
         </is>
       </c>
-      <c r="CE27" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
-      <c r="CF27" t="inlineStr">
-        <is>
-          <t>52.1</t>
-        </is>
-      </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -12063,12 +12063,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>274.793</t>
+          <t>312.769</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -12088,17 +12088,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-39.35</t>
+          <t>-42.41</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -12163,7 +12163,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-14.96</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -12173,17 +12173,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -12194,73 +12194,73 @@
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>37.04</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-5.59</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>51.73999999999999</t>
+          <t>51.86</t>
         </is>
       </c>
       <c r="AM28" t="n">
-        <v>55.01</v>
+        <v>54.78</v>
       </c>
       <c r="AN28" t="n">
-        <v>58.25</v>
+        <v>58.02</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>58.78</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>-19.37</t>
+          <t>-11.93</t>
         </is>
       </c>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
@@ -12270,7 +12270,7 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>-121.72</t>
+          <t>-122.39</t>
         </is>
       </c>
       <c r="AU28" t="inlineStr">
@@ -12280,43 +12280,43 @@
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>331265030.4933921</t>
+          <t>330804763.1502933</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>14210191.0</t>
+          <t>16370637.0</t>
         </is>
       </c>
       <c r="AX28" t="n">
-        <v>15743790.2</v>
+        <v>14968564.6</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>25956465.7</t>
+          <t>25991927.5</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>65312254.98</v>
+        <v>55328963.9</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>-10212675</t>
+          <t>-11023362</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>-3722008.688945839</t>
+          <t>-3728120.943557476</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>-3880161.860334959</t>
+          <t>-3761738.343921479</t>
         </is>
       </c>
       <c r="BD28" t="inlineStr">
         <is>
-          <t>14210191.0</t>
+          <t>16370637.0</t>
         </is>
       </c>
       <c r="BE28" t="inlineStr">
@@ -12336,7 +12336,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-10.45</t>
         </is>
       </c>
       <c r="BI28" t="inlineStr">
@@ -12381,7 +12381,7 @@
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
@@ -12391,7 +12391,7 @@
       </c>
       <c r="BS28" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BT28" t="inlineStr">
@@ -12421,7 +12421,7 @@
       </c>
       <c r="BY28" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ28" t="inlineStr">
@@ -12446,22 +12446,22 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
         <is>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="CF28" t="inlineStr">
+        <is>
           <t>52.1</t>
         </is>
       </c>
-      <c r="CF28" t="inlineStr">
-        <is>
-          <t>51.4</t>
-        </is>
-      </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -12493,12 +12493,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>307.156</t>
+          <t>274.793</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -12508,7 +12508,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -12518,17 +12518,17 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-16.89</t>
+          <t>-39.35</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -12593,7 +12593,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>-16.59</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -12603,17 +12603,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -12624,42 +12624,42 @@
       <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
@@ -12668,29 +12668,29 @@
         </is>
       </c>
       <c r="AM29" t="n">
-        <v>55.27</v>
+        <v>55.01</v>
       </c>
       <c r="AN29" t="n">
-        <v>58.46</v>
+        <v>58.25</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>-26.31</t>
+          <t>-19.37</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
@@ -12700,7 +12700,7 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>-120.67</t>
+          <t>-121.72</t>
         </is>
       </c>
       <c r="AU29" t="inlineStr">
@@ -12710,43 +12710,43 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>331265030.4933921</t>
+          <t>330804763.1502933</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>15825778.0</t>
+          <t>14210191.0</t>
         </is>
       </c>
       <c r="AX29" t="n">
-        <v>21316600.4</v>
+        <v>15743790.2</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>25649746.9</t>
+          <t>25956465.7</t>
         </is>
       </c>
       <c r="AZ29" t="n">
-        <v>67714501.66</v>
+        <v>65312254.98</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>-4333146</t>
+          <t>-10212675</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>-3693253.56687509</t>
+          <t>-3722008.688945839</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>-3679284.745913677</t>
+          <t>-3880161.860334959</t>
         </is>
       </c>
       <c r="BD29" t="inlineStr">
         <is>
-          <t>15825778.0</t>
+          <t>14210191.0</t>
         </is>
       </c>
       <c r="BE29" t="inlineStr">
@@ -12766,7 +12766,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>-12.16</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="BI29" t="inlineStr">
@@ -12811,7 +12811,7 @@
       </c>
       <c r="BQ29" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR29" t="inlineStr">
@@ -12821,7 +12821,7 @@
       </c>
       <c r="BS29" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BT29" t="inlineStr">
@@ -12851,7 +12851,7 @@
       </c>
       <c r="BY29" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ29" t="inlineStr">
@@ -12876,22 +12876,22 @@
       </c>
       <c r="CD29" t="inlineStr">
         <is>
+          <t>52.0</t>
+        </is>
+      </c>
+      <c r="CE29" t="inlineStr">
+        <is>
+          <t>52.1</t>
+        </is>
+      </c>
+      <c r="CF29" t="inlineStr">
+        <is>
+          <t>51.4</t>
+        </is>
+      </c>
+      <c r="CG29" t="inlineStr">
+        <is>
           <t>51.9</t>
-        </is>
-      </c>
-      <c r="CE29" t="inlineStr">
-        <is>
-          <t>51.9</t>
-        </is>
-      </c>
-      <c r="CF29" t="inlineStr">
-        <is>
-          <t>51.3</t>
-        </is>
-      </c>
-      <c r="CG29" t="inlineStr">
-        <is>
-          <t>51.3</t>
         </is>
       </c>
       <c r="CH29" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>330.94</t>
+          <t>307.156</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -12953,12 +12953,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-15.04</t>
+          <t>-16.89</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -13033,17 +13033,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -13054,12 +13054,12 @@
       <c r="AC30" t="inlineStr"/>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
@@ -13074,53 +13074,53 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>52.14</t>
+          <t>51.73999999999999</t>
         </is>
       </c>
       <c r="AM30" t="n">
-        <v>55.59</v>
+        <v>55.27</v>
       </c>
       <c r="AN30" t="n">
-        <v>58.66</v>
+        <v>58.46</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>58.97</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>-30.14</t>
+          <t>-26.31</t>
         </is>
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
@@ -13130,7 +13130,7 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>-119.31</t>
+          <t>-120.67</t>
         </is>
       </c>
       <c r="AU30" t="inlineStr">
@@ -13140,43 +13140,43 @@
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>331265030.4933921</t>
+          <t>330804763.1502933</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>17027345.0</t>
+          <t>15825778.0</t>
         </is>
       </c>
       <c r="AX30" t="n">
-        <v>22754558</v>
+        <v>21316600.4</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>26782636.3</t>
+          <t>25649746.9</t>
         </is>
       </c>
       <c r="AZ30" t="n">
-        <v>69191727.59999999</v>
+        <v>67714501.66</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>-4028078</t>
+          <t>-4333146</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>-3695793.352504438</t>
+          <t>-3693253.56687509</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>-3434013.020100649</t>
+          <t>-3679284.745913677</t>
         </is>
       </c>
       <c r="BD30" t="inlineStr">
         <is>
-          <t>17027345.0</t>
+          <t>15825778.0</t>
         </is>
       </c>
       <c r="BE30" t="inlineStr">
@@ -13281,7 +13281,7 @@
       </c>
       <c r="BY30" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ30" t="inlineStr">
@@ -13306,17 +13306,17 @@
       </c>
       <c r="CD30" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CE30" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CF30" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CG30" t="inlineStr">
@@ -13353,12 +13353,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>217.689</t>
+          <t>330.94</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -13368,7 +13368,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -13378,17 +13378,17 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>-15.04</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>-14.63</t>
+          <t>-16.59</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -13463,17 +13463,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -13484,17 +13484,17 @@
       <c r="AC31" t="inlineStr"/>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr">
@@ -13504,53 +13504,53 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>52.67999999999999</t>
+          <t>52.14</t>
         </is>
       </c>
       <c r="AM31" t="n">
-        <v>55.92</v>
+        <v>55.59</v>
       </c>
       <c r="AN31" t="n">
-        <v>58.83</v>
+        <v>58.66</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>59.06</t>
+          <t>58.97</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>-31.69</t>
+          <t>-30.14</t>
         </is>
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
@@ -13560,7 +13560,7 @@
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>-117.86</t>
+          <t>-119.31</t>
         </is>
       </c>
       <c r="AU31" t="inlineStr">
@@ -13570,43 +13570,43 @@
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>331265030.4933921</t>
+          <t>330804763.1502933</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>11408872.0</t>
+          <t>17027345.0</t>
         </is>
       </c>
       <c r="AX31" t="n">
-        <v>28718377.4</v>
+        <v>22754558</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>27355481.5</t>
+          <t>26782636.3</t>
         </is>
       </c>
       <c r="AZ31" t="n">
-        <v>69373581.34</v>
+        <v>69191727.59999999</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>1362895</t>
+          <t>-4028078</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>-3743389.776577854</t>
+          <t>-3695793.352504438</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>-3089720.839649871</t>
+          <t>-3434013.020100649</t>
         </is>
       </c>
       <c r="BD31" t="inlineStr">
         <is>
-          <t>11408872.0</t>
+          <t>17027345.0</t>
         </is>
       </c>
       <c r="BE31" t="inlineStr">
@@ -13626,7 +13626,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>-10.10</t>
+          <t>-12.16</t>
         </is>
       </c>
       <c r="BI31" t="inlineStr">
@@ -13671,17 +13671,17 @@
       </c>
       <c r="BQ31" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR31" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS31" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="BT31" t="inlineStr">
@@ -13711,7 +13711,7 @@
       </c>
       <c r="BY31" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ31" t="inlineStr">
@@ -13736,22 +13736,22 @@
       </c>
       <c r="CD31" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CE31" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CF31" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CG31" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CH31" t="inlineStr">
@@ -13783,12 +13783,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>392.184</t>
+          <t>217.689</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -13798,7 +13798,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -13808,17 +13808,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>28.13</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -13883,7 +13883,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>-15.93</t>
+          <t>-14.63</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
@@ -13893,17 +13893,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -13914,73 +13914,73 @@
       <c r="AC32" t="inlineStr"/>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.33</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>-5.37</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>53.23999999999999</t>
+          <t>52.67999999999999</t>
         </is>
       </c>
       <c r="AM32" t="n">
-        <v>56.26</v>
+        <v>55.92</v>
       </c>
       <c r="AN32" t="n">
-        <v>58.96</v>
+        <v>58.83</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>59.09</t>
+          <t>59.06</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>-38.48</t>
+          <t>-31.69</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr">
@@ -13990,7 +13990,7 @@
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>-116.44</t>
+          <t>-117.86</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
@@ -14000,43 +14000,43 @@
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>331265030.4933921</t>
+          <t>330804763.1502933</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>20246765.0</t>
+          <t>11408872.0</t>
         </is>
       </c>
       <c r="AX32" t="n">
-        <v>37015290.4</v>
+        <v>28718377.4</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>28888889.5</t>
+          <t>27355481.5</t>
         </is>
       </c>
       <c r="AZ32" t="n">
-        <v>69945836.02</v>
+        <v>69373581.34</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>8126400</t>
+          <t>1362895</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>-3862238.674201123</t>
+          <t>-3743389.776577854</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>-1885548.444732688</t>
+          <t>-3089720.839649871</t>
         </is>
       </c>
       <c r="BD32" t="inlineStr">
         <is>
-          <t>20246765.0</t>
+          <t>11408872.0</t>
         </is>
       </c>
       <c r="BE32" t="inlineStr">
@@ -14056,7 +14056,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>-11.47</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="BI32" t="inlineStr">
@@ -14101,17 +14101,17 @@
       </c>
       <c r="BQ32" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR32" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS32" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT32" t="inlineStr">
@@ -14141,7 +14141,7 @@
       </c>
       <c r="BY32" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ32" t="inlineStr">
@@ -14166,22 +14166,22 @@
       </c>
       <c r="CD32" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CE32" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CF32" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CG32" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH32" t="inlineStr">
@@ -14213,12 +14213,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>804.698</t>
+          <t>392.184</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -14228,7 +14228,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -14238,17 +14238,17 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>28.13</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -14313,7 +14313,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-15.93</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -14323,17 +14323,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -14344,12 +14344,12 @@
       <c r="AC33" t="inlineStr"/>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
@@ -14364,53 +14364,53 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-5.37</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>54.21999999999999</t>
+          <t>53.23999999999999</t>
         </is>
       </c>
       <c r="AM33" t="n">
-        <v>56.57</v>
+        <v>56.26</v>
       </c>
       <c r="AN33" t="n">
-        <v>59.12</v>
+        <v>58.96</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>59.15</t>
+          <t>59.09</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>-37.13</t>
+          <t>-38.48</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr">
@@ -14420,7 +14420,7 @@
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>-114.86</t>
+          <t>-116.44</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
@@ -14430,43 +14430,43 @@
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>331265030.4933921</t>
+          <t>330804763.1502933</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>42074242.0</t>
+          <t>20246765.0</t>
         </is>
       </c>
       <c r="AX33" t="n">
-        <v>36169141.2</v>
+        <v>37015290.4</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>29060387.7</t>
+          <t>28888889.5</t>
         </is>
       </c>
       <c r="AZ33" t="n">
-        <v>70323701.58</v>
+        <v>69945836.02</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>7108753</t>
+          <t>8126400</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>-4221636.897740839</t>
+          <t>-3862238.674201123</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>-1044878.257539123</t>
+          <t>-1885548.444732688</t>
         </is>
       </c>
       <c r="BD33" t="inlineStr">
         <is>
-          <t>42074242.0</t>
+          <t>20246765.0</t>
         </is>
       </c>
       <c r="BE33" t="inlineStr">
@@ -14486,7 +14486,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-11.47</t>
         </is>
       </c>
       <c r="BI33" t="inlineStr">
@@ -14531,7 +14531,7 @@
       </c>
       <c r="BQ33" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR33" t="inlineStr">
@@ -14541,7 +14541,7 @@
       </c>
       <c r="BS33" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="BT33" t="inlineStr">
@@ -14571,7 +14571,7 @@
       </c>
       <c r="BY33" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ33" t="inlineStr">
@@ -14596,22 +14596,22 @@
       </c>
       <c r="CD33" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CE33" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CF33" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CG33" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CH33" t="inlineStr">
@@ -14643,12 +14643,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>429.632</t>
+          <t>804.698</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -14658,7 +14658,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -14668,17 +14668,17 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -14743,7 +14743,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
@@ -14753,17 +14753,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -14774,12 +14774,12 @@
       <c r="AC34" t="inlineStr"/>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
@@ -14794,53 +14794,53 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>55.12</t>
+          <t>54.21999999999999</t>
         </is>
       </c>
       <c r="AM34" t="n">
-        <v>56.86</v>
+        <v>56.57</v>
       </c>
       <c r="AN34" t="n">
-        <v>59.28</v>
+        <v>59.12</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>59.15</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>-28.39</t>
+          <t>-37.13</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
@@ -14850,7 +14850,7 @@
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>-113.48</t>
+          <t>-114.86</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
@@ -14860,43 +14860,43 @@
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>331265030.4933921</t>
+          <t>330804763.1502933</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>23015566.0</t>
+          <t>42074242.0</t>
         </is>
       </c>
       <c r="AX34" t="n">
-        <v>29982893.4</v>
+        <v>36169141.2</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>27325142.8</t>
+          <t>29060387.7</t>
         </is>
       </c>
       <c r="AZ34" t="n">
-        <v>70871687.59999999</v>
+        <v>70323701.58</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>2657750</t>
+          <t>7108753</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>-4799229.377777515</t>
+          <t>-4221636.897740839</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>-2145262.016636197</t>
+          <t>-1044878.257539123</t>
         </is>
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>23015566.0</t>
+          <t>42074242.0</t>
         </is>
       </c>
       <c r="BE34" t="inlineStr">
@@ -14916,7 +14916,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="BI34" t="inlineStr">
@@ -14961,7 +14961,7 @@
       </c>
       <c r="BQ34" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR34" t="inlineStr">
@@ -14971,7 +14971,7 @@
       </c>
       <c r="BS34" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BT34" t="inlineStr">
@@ -15001,7 +15001,7 @@
       </c>
       <c r="BY34" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ34" t="inlineStr">
@@ -15026,22 +15026,22 @@
       </c>
       <c r="CD34" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CE34" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CF34" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CG34" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CH34" t="inlineStr">

--- a/Result/checksun_type/商業應用.xlsx
+++ b/Result/checksun_type/商業應用.xlsx
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8665.119</t>
+          <t>7415.68</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>8.17</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-27.26</t>
+          <t>-27.85</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>8665</t>
+          <t>7416</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1159,51 +1159,51 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>15.83</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>-0.39</v>
+        <v>-0.92</v>
       </c>
       <c r="AV2" t="n">
-        <v>-1.42</v>
+        <v>-1.54</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>-7.70</t>
+          <t>-7.34</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>49.29</t>
+          <t>49.15000000000001</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>50</v>
+        <v>49.92</v>
       </c>
       <c r="BA2" t="n">
-        <v>49.83</v>
+        <v>49.77</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>53.99</t>
+          <t>53.72</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>-14.84</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>-0.32</v>
+        <v>-0.36</v>
       </c>
       <c r="BE2" t="n">
-        <v>-0.3</v>
+        <v>-0.31</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-104.24</t>
+          <t>-104.40</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,43 +1222,43 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>1123200425.188965</t>
+          <t>1122403185.247934</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>427954763.0</t>
+          <t>362936152.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>325721487.2</v>
+        <v>352004775</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>310571810.3</t>
+          <t>325429529.5</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>559313467.14</v>
+        <v>559701265.1799999</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>15149676</t>
+          <t>26575245</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-48811915.64742068</t>
+          <t>-47914257.18953548</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-49107955.80871153</t>
+          <t>-42977135.6711669</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>427954763.0</t>
+          <t>362936152.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>30.67</t>
+          <t>30.78</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>41015</t>
+          <t>40711</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>48.95</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4595.698</t>
+          <t>8665.119</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-27.04</t>
+          <t>-27.26</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1631,67 +1631,67 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>8665</t>
+          <t>7416</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>36.26</t>
+          <t>15.83</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>-0.16</v>
+        <v>-0.39</v>
       </c>
       <c r="AV3" t="n">
-        <v>-1.35</v>
+        <v>-1.42</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>-8.07</t>
+          <t>-7.70</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.29</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>50.01</v>
+        <v>50</v>
       </c>
       <c r="BA3" t="n">
-        <v>49.9</v>
+        <v>49.83</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>54.28</t>
+          <t>53.99</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="BD3" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="BE3" t="n">
         <v>-0.3</v>
       </c>
-      <c r="BE3" t="n">
-        <v>-0.29</v>
-      </c>
       <c r="BF3" t="inlineStr">
         <is>
           <t>7.04</t>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-104.17</t>
+          <t>-104.24</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,43 +1709,43 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>1123200425.188965</t>
+          <t>1122403185.247934</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>227387122.0</t>
+          <t>427954763.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>312176737.6</v>
+        <v>325721487.2</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>292619981.8</t>
+          <t>310571810.3</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>558800828.6</v>
+        <v>559313467.14</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>19556755</t>
+          <t>15149676</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-48758090.16354962</t>
+          <t>-48811915.64742068</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-63078694.47632128</t>
+          <t>-49107955.80871153</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>227387122.0</t>
+          <t>427954763.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>30.67</t>
+          <t>30.78</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>41015</t>
+          <t>40711</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>48.95</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>7402.298</t>
+          <t>4595.698</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,149 +1937,149 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>49.25</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-1.13</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>6.68</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-07-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-01-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-02-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>41.8</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>67.5</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>48.8</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>48.05</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>-27.04</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>-13.01</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025/07/24</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>40.1</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>-0.0</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>52.0</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>2025/07/03</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>39.1</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>2025/12/31</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
           <t>49.2</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-0.2</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>11.12</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-07-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-01-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-02-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>41.8</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>67.5</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>48.8</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>48.05</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>-27.11</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>-13.01</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2025/07/24</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>40.1</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2025/10/20</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>52.0</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>2025/07/03</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>39.1</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>2025/12/31</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>49.2</t>
-        </is>
-      </c>
       <c r="AI4" t="inlineStr">
         <is>
           <t>2025/12/19</t>
@@ -2097,17 +2097,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2118,59 +2118,59 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>8665</t>
+          <t>7416</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>41.94</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>52.69</t>
+          <t>36.26</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>-0.61</v>
+        <v>-0.16</v>
       </c>
       <c r="AV4" t="n">
-        <v>-1.01</v>
+        <v>-1.35</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>-8.42</t>
+          <t>-8.07</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.33</t>
         </is>
       </c>
       <c r="AZ4" t="n">
         <v>50.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>49.97</v>
+        <v>49.9</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>54.57</t>
+          <t>54.28</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="BD4" t="n">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-104.14</t>
+          <t>-104.17</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,43 +2196,43 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>1123200425.188965</t>
+          <t>1122403185.247934</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>367305573.0</t>
+          <t>227387122.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>351182388.8</v>
+        <v>312176737.6</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>316039524.0</t>
+          <t>292619981.8</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>565105616.1</v>
+        <v>558800828.6</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>35142864</t>
+          <t>19556755</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-46154343.92486387</t>
+          <t>-48758090.16354962</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-59294691.94875234</t>
+          <t>-63078694.47632128</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>367305573.0</t>
+          <t>227387122.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>30.67</t>
+          <t>30.78</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>41015</t>
+          <t>40711</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2399,7 +2399,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7606.86</t>
+          <t>7402.298</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>11.12</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-26.67</t>
+          <t>-27.11</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2605,63 +2605,63 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>8665</t>
+          <t>7416</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>61.29</t>
+          <t>41.94</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>54.84</t>
+          <t>52.69</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>-0.22</v>
+        <v>-0.61</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.73</v>
+        <v>-1.01</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>-8.85</t>
+          <t>-8.42</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>49.61</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="AZ5" t="n">
+        <v>50.01</v>
+      </c>
+      <c r="BA5" t="n">
         <v>49.97</v>
       </c>
-      <c r="BA5" t="n">
-        <v>50.02</v>
-      </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>54.88</t>
+          <t>54.57</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>-0.28</v>
+        <v>-0.3</v>
       </c>
       <c r="BE5" t="n">
         <v>-0.29</v>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-104.13</t>
+          <t>-104.14</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,43 +2683,43 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>1123200425.188965</t>
+          <t>1122403185.247934</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>374440265.0</t>
+          <t>367305573.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>326170285.2</v>
+        <v>351182388.8</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>326382939.2</t>
+          <t>316039524.0</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>567766091.96</v>
+        <v>565105616.1</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-212654</t>
+          <t>35142864</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-43765189.73870233</t>
+          <t>-46154343.92486387</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-66762569.08976984</t>
+          <t>-59294691.94875234</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>374440265.0</t>
+          <t>367305573.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>30.67</t>
+          <t>30.78</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>41015</t>
+          <t>40711</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4655.284</t>
+          <t>7606.86</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-7.64</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-26.81</t>
+          <t>-26.67</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3092,59 +3092,59 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>8665</t>
+          <t>7416</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
+          <t>61.29</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
           <t>54.84</t>
         </is>
       </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>55.5</t>
-        </is>
-      </c>
       <c r="AU6" t="n">
-        <v>-0.6</v>
+        <v>-0.22</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.49</v>
+        <v>-0.73</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>-9.21</t>
+          <t>-8.85</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.61</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>49.94</v>
+        <v>49.97</v>
       </c>
       <c r="BA6" t="n">
-        <v>50.07</v>
+        <v>50.02</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>55.15</t>
+          <t>54.88</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="BD6" t="n">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-104.18</t>
+          <t>-104.13</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,43 +3170,43 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>1123200425.188965</t>
+          <t>1122403185.247934</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>231519713.0</t>
+          <t>374440265.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>298854284</v>
+        <v>326170285.2</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>323592464.3</t>
+          <t>326382939.2</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>574595797.84</v>
+        <v>567766091.96</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-24738180</t>
+          <t>-212654</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-39583848.03850824</t>
+          <t>-43765189.73870233</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-75811018.8237316</t>
+          <t>-66762569.08976984</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>231519713.0</t>
+          <t>374440265.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>30.67</t>
+          <t>30.78</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>41015</t>
+          <t>40711</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>49.65</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7238.561</t>
+          <t>4655.284</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,159 +3398,159 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>49.4</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-1.44</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-7.64</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-07-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-01-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-02-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>41.8</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>67.5</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>48.8</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>48.05</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>-26.81</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>-13.01</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025/07/24</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>40.1</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>52.0</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>2025/07/03</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>39.1</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>2025/12/31</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>49.2</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>2025/12/19</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
           <t>49.3</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>-0.41</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>-23.40</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-07-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-01-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-02-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>41.8</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>67.5</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>48.8</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>48.05</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>-26.96</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>-13.01</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2025/07/24</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>40.1</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2025/10/20</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>52.0</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>2025/07/03</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>39.1</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>2025/12/31</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>49.2</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>2025/12/19</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>49.3</t>
-        </is>
-      </c>
       <c r="AK7" t="inlineStr">
         <is>
           <t>2025-12-11 00:00:00</t>
@@ -3558,17 +3558,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3579,66 +3579,66 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>8665</t>
+          <t>7416</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>48.39</t>
+          <t>54.84</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>48.81</t>
+          <t>55.5</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>-0.76</v>
+        <v>-0.6</v>
       </c>
       <c r="AV7" t="n">
-        <v>-0.59</v>
+        <v>-0.49</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>-9.56</t>
+          <t>-9.21</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>49.68</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>49.97</v>
+        <v>49.94</v>
       </c>
       <c r="BA7" t="n">
-        <v>50.14</v>
+        <v>50.07</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>55.44</t>
+          <t>55.15</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>-0.27</v>
+        <v>-0.28</v>
       </c>
       <c r="BE7" t="n">
-        <v>-0.3</v>
+        <v>-0.29</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-104.22</t>
+          <t>-104.18</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,43 +3657,43 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>1123200425.188965</t>
+          <t>1122403185.247934</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>360231015.0</t>
+          <t>231519713.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>295422133.4</v>
+        <v>298854284</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>385653258.8</t>
+          <t>323592464.3</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>582817319.28</v>
+        <v>574595797.84</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-90231125</t>
+          <t>-24738180</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-32997089.71392217</t>
+          <t>-39583848.03850824</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-70716922.91425806</t>
+          <t>-75811018.8237316</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>360231015.0</t>
+          <t>231519713.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>30.67</t>
+          <t>30.78</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>41015</t>
+          <t>40711</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>49.65</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8384.386</t>
+          <t>7238.561</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-42.79</t>
+          <t>-23.40</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-25.78</t>
+          <t>-26.96</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4066,63 +4066,63 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>8665</t>
+          <t>7416</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>63.27</t>
+          <t>48.39</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>46.21</t>
+          <t>48.81</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>1.15</v>
+        <v>-0.76</v>
       </c>
       <c r="AV8" t="n">
-        <v>-0.87</v>
+        <v>-0.59</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>-9.84</t>
+          <t>-9.56</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>49.53</t>
+          <t>49.68</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>49.96</v>
+        <v>49.97</v>
       </c>
       <c r="BA8" t="n">
-        <v>50.22</v>
+        <v>50.14</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>55.44</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>20.24</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>-0.24</v>
+        <v>-0.27</v>
       </c>
       <c r="BE8" t="n">
         <v>-0.3</v>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-104.32</t>
+          <t>-104.22</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,43 +4144,43 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>1123200425.188965</t>
+          <t>1122403185.247934</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>422415378.0</t>
+          <t>360231015.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>273063226</v>
+        <v>295422133.4</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>477294231.4</t>
+          <t>385653258.8</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>589099067.22</v>
+        <v>582817319.28</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-204231005</t>
+          <t>-90231125</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-26138938.22295201</t>
+          <t>-32997089.71392217</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-74704535.29664373</t>
+          <t>-70716922.91425806</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>422415378.0</t>
+          <t>360231015.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>30.67</t>
+          <t>30.78</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>41015</t>
+          <t>40711</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4833.399</t>
+          <t>8384.386</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>49.75</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-58.10</t>
+          <t>-42.79</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-26.30</t>
+          <t>-25.78</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4553,66 +4553,66 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>8665</t>
+          <t>7416</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>34.78</t>
+          <t>63.27</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>32.37</t>
+          <t>46.21</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>0.71</v>
+        <v>1.15</v>
       </c>
       <c r="AV9" t="n">
-        <v>-1.03</v>
+        <v>-0.87</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>-10.10</t>
+          <t>-9.84</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>49.53</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>49.91</v>
+        <v>49.96</v>
       </c>
       <c r="BA9" t="n">
-        <v>50.26</v>
+        <v>50.22</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>55.91</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>10.56</t>
+          <t>20.24</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>-0.29</v>
+        <v>-0.24</v>
       </c>
       <c r="BE9" t="n">
-        <v>-0.32</v>
+        <v>-0.3</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-104.54</t>
+          <t>-104.32</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,43 +4631,43 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>1123200425.188965</t>
+          <t>1122403185.247934</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>242245055.0</t>
+          <t>422415378.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>280896659.2</v>
+        <v>273063226</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>670333148.7</t>
+          <t>477294231.4</t>
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>607838296.98</v>
+        <v>589099067.22</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-389436489</t>
+          <t>-204231005</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-17308829.66409897</t>
+          <t>-26138938.22295201</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-84395715.61802888</t>
+          <t>-74704535.29664373</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>242245055.0</t>
+          <t>422415378.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>30.67</t>
+          <t>30.78</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>41015</t>
+          <t>40711</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4797,22 +4797,22 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>49.75</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>49.75</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4766.325</t>
+          <t>4833.399</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>49.75</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-55.81</t>
+          <t>-58.10</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-26.00</t>
+          <t>-26.30</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5040,66 +5040,66 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>8665</t>
+          <t>7416</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>40.58</t>
+          <t>34.78</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>20.77</t>
+          <t>32.37</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>1.26</v>
+        <v>0.71</v>
       </c>
       <c r="AV10" t="n">
         <v>-1.03</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>-10.23</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>49.84</v>
+        <v>49.91</v>
       </c>
       <c r="BA10" t="n">
-        <v>50.36</v>
+        <v>50.26</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>56.09</t>
+          <t>55.91</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>8.18</t>
+          <t>10.56</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>-0.3</v>
+        <v>-0.29</v>
       </c>
       <c r="BE10" t="n">
-        <v>-0.33</v>
+        <v>-0.32</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-104.66</t>
+          <t>-104.54</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,43 +5118,43 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>1123200425.188965</t>
+          <t>1122403185.247934</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>237860259.0</t>
+          <t>242245055.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>326595593.2</v>
+        <v>280896659.2</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>739036679.0</t>
+          <t>670333148.7</t>
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>622138646.22</v>
+        <v>607838296.98</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-412441085</t>
+          <t>-389436489</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-5111214.036111711</t>
+          <t>-17308829.66409897</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-75922163.05507797</t>
+          <t>-84395715.61802888</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>237860259.0</t>
+          <t>242245055.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>30.67</t>
+          <t>30.78</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>41015</t>
+          <t>40711</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>49.75</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>49.75</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>208.185</t>
+          <t>140.592</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>9.90</t>
+          <t>15.67</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-12.61</t>
+          <t>-12.02</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5506,17 +5506,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5527,66 +5527,66 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>141</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>-1.52</v>
+        <v>-0.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.88</v>
+        <v>0.63</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>151.3</t>
+          <t>150.9</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>149.98</v>
+        <v>149.95</v>
       </c>
       <c r="BA11" t="n">
-        <v>152.31</v>
+        <v>152.03</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>159.11</t>
+          <t>158.88</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>52.39</t>
+          <t>44.54</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>-0.35</v>
+        <v>-0.37</v>
       </c>
       <c r="BE11" t="n">
-        <v>-0.74</v>
+        <v>-0.67</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-111.25</t>
+          <t>-110.12</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,43 +5605,43 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>84393600.5937931</t>
+          <t>84320789.57231405</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>31159997.0</t>
+          <t>21021866.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>18888488.6</v>
+        <v>19809081.8</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>17186891.2</t>
+          <t>17125925.9</t>
         </is>
       </c>
       <c r="BM11" t="n">
-        <v>26961282.46</v>
+        <v>26838636.86</v>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>1701597</t>
+          <t>2683155</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-1386966.730689016</t>
+          <t>-1100988.908149415</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>359953.39171822</t>
+          <t>471889.1158183888</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>31159997.0</t>
+          <t>21021866.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>-6.88</t>
+          <t>-6.25</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5706,22 +5706,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>18.84</t>
+          <t>18.96</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>27.49</t>
+          <t>27.78</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>15848</t>
+          <t>15954</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>118.818</t>
+          <t>208.185</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5843,167 +5843,167 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
+          <t>0.67</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-1.12</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>9.90</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-09-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-08-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-08-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>171.5</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>170.5</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>167.5</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>173.5</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>-12.61</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>-1.15</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025/05/13</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>164.5</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2025/09/23</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>171.5</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>2025/07/02</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>158.5</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>2025/10/13</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>170.5</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>2025/08/21</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>173.5</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>2025-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>3.91</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
           <t>-2.35</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>-0.59</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-09-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-08-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-08-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>171.5</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>170.5</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>167.5</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>173.5</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>-10.56</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>-1.15</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2025/05/13</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>164.5</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>2025/09/23</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>171.5</t>
-        </is>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>2025/07/02</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>158.5</t>
-        </is>
-      </c>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t>2025/10/13</t>
-        </is>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>170.5</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>2025/08/21</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>173.5</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>2025-09-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>2026-01-02</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>2.23</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>0.34</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6014,66 +6014,66 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>141</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>90.48</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>0.73</v>
+        <v>-1.52</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>151.4</t>
+          <t>151.3</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>150.05</v>
+        <v>149.98</v>
       </c>
       <c r="BA12" t="n">
-        <v>152.58</v>
+        <v>152.31</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>159.37</t>
+          <t>159.11</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>73.22</t>
+          <t>52.39</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>-0.22</v>
+        <v>-0.35</v>
       </c>
       <c r="BE12" t="n">
-        <v>-0.84</v>
+        <v>-0.74</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-112.72</t>
+          <t>-111.25</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6092,43 +6092,43 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>84393600.5937931</t>
+          <t>84320789.57231405</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>18115281.0</t>
+          <t>31159997.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>15285464.4</v>
+        <v>18888488.6</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>15376128.5</t>
+          <t>17186891.2</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>27396559.88</v>
+        <v>26961282.46</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-90664</t>
+          <t>1701597</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-1704588.571126695</t>
+          <t>-1386966.730689016</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>-899038.5852719601</t>
+          <t>359953.39171822</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>18115281.0</t>
+          <t>31159997.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-6.88</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -6193,24 +6193,24 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
+          <t>4.83</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
+        <is>
           <t>4.95</t>
         </is>
       </c>
-      <c r="CG12" t="inlineStr">
-        <is>
-          <t>4.98</t>
-        </is>
-      </c>
       <c r="CH12" t="inlineStr">
         <is>
           <t>18.41</t>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>18.84</t>
+          <t>18.96</t>
         </is>
       </c>
       <c r="CJ12" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>27.49</t>
+          <t>27.78</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>15848</t>
+          <t>15954</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
@@ -6258,22 +6258,22 @@
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>151.5</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>153.5</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">
@@ -6305,12 +6305,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>115.634</t>
+          <t>118.818</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6330,17 +6330,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-6.00</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-11.44</t>
+          <t>-10.56</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -6480,17 +6480,17 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -6501,17 +6501,17 @@
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>141</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
@@ -6520,247 +6520,247 @@
         </is>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.68</v>
+        <v>0.9</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
+          <t>151.4</t>
+        </is>
+      </c>
+      <c r="AZ13" t="n">
+        <v>150.05</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>152.58</v>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>159.37</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>73.22</t>
+        </is>
+      </c>
+      <c r="BD13" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>-0.84</v>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>6.61</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>-112.72</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>2025/11/26</t>
+        </is>
+      </c>
+      <c r="BI13" t="inlineStr">
+        <is>
+          <t>84320789.57231405</t>
+        </is>
+      </c>
+      <c r="BJ13" t="inlineStr">
+        <is>
+          <t>18115281.0</t>
+        </is>
+      </c>
+      <c r="BK13" t="n">
+        <v>15285464.4</v>
+      </c>
+      <c r="BL13" t="inlineStr">
+        <is>
+          <t>15376128.5</t>
+        </is>
+      </c>
+      <c r="BM13" t="n">
+        <v>27396559.88</v>
+      </c>
+      <c r="BN13" t="inlineStr">
+        <is>
+          <t>-90664</t>
+        </is>
+      </c>
+      <c r="BO13" t="inlineStr">
+        <is>
+          <t>-1704588.571126695</t>
+        </is>
+      </c>
+      <c r="BP13" t="inlineStr">
+        <is>
+          <t>-899038.5852719601</t>
+        </is>
+      </c>
+      <c r="BQ13" t="inlineStr">
+        <is>
+          <t>18115281.0</t>
+        </is>
+      </c>
+      <c r="BR13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS13" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
+      <c r="BT13" t="inlineStr">
+        <is>
+          <t>2025/07/24</t>
+        </is>
+      </c>
+      <c r="BU13" t="inlineStr">
+        <is>
+          <t>-4.69</t>
+        </is>
+      </c>
+      <c r="BV13" t="inlineStr">
+        <is>
+          <t>敦陽科</t>
+        </is>
+      </c>
+      <c r="BW13" t="inlineStr">
+        <is>
+          <t>敦陽科</t>
+        </is>
+      </c>
+      <c r="BX13" t="inlineStr">
+        <is>
+          <t>資訊服務業</t>
+        </is>
+      </c>
+      <c r="BY13" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BZ13" t="inlineStr">
+        <is>
+          <t>0.67</t>
+        </is>
+      </c>
+      <c r="CA13" t="inlineStr">
+        <is>
+          <t>-12.58214103619475</t>
+        </is>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>1.043189390647018</t>
+        </is>
+      </c>
+      <c r="CC13" t="inlineStr">
+        <is>
+          <t>13.35381850712726</t>
+        </is>
+      </c>
+      <c r="CD13" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE13" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CF13" t="inlineStr">
+        <is>
+          <t>4.95</t>
+        </is>
+      </c>
+      <c r="CG13" t="inlineStr">
+        <is>
+          <t>4.95</t>
+        </is>
+      </c>
+      <c r="CH13" t="inlineStr">
+        <is>
+          <t>18.41</t>
+        </is>
+      </c>
+      <c r="CI13" t="inlineStr">
+        <is>
+          <t>18.96</t>
+        </is>
+      </c>
+      <c r="CJ13" t="inlineStr">
+        <is>
+          <t>24.79%</t>
+        </is>
+      </c>
+      <c r="CK13" t="inlineStr">
+        <is>
+          <t>12.14%</t>
+        </is>
+      </c>
+      <c r="CL13" t="inlineStr">
+        <is>
+          <t>27.78</t>
+        </is>
+      </c>
+      <c r="CM13" t="inlineStr">
+        <is>
+          <t>15954</t>
+        </is>
+      </c>
+      <c r="CN13" t="inlineStr">
+        <is>
+          <t>諮詢與維修服務31.76%、電腦軟體19.44%、網路產品17.90%、儲存設備16.51%、工作站及伺服器主機10.52%、電腦周邊產品3.19%、個人電腦(PC)0.57%、其他0.11% (2024年)</t>
+        </is>
+      </c>
+      <c r="CO13" t="inlineStr">
+        <is>
+          <t>敦陽科-資訊服務業-上市</t>
+        </is>
+      </c>
+      <c r="CP13" t="inlineStr">
+        <is>
+          <t>資訊服務業右上上市</t>
+        </is>
+      </c>
+      <c r="CQ13" t="inlineStr">
+        <is>
+          <t>151.5</t>
+        </is>
+      </c>
+      <c r="CR13" t="inlineStr">
+        <is>
+          <t>153.5</t>
+        </is>
+      </c>
+      <c r="CS13" t="inlineStr">
+        <is>
           <t>151.0</t>
         </is>
       </c>
-      <c r="AZ13" t="n">
-        <v>149.98</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>152.82</v>
-      </c>
-      <c r="BB13" t="inlineStr">
-        <is>
-          <t>159.57</t>
-        </is>
-      </c>
-      <c r="BC13" t="inlineStr">
-        <is>
-          <t>58.36</t>
-        </is>
-      </c>
-      <c r="BD13" t="n">
-        <v>-0.41</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>-0.99</v>
-      </c>
-      <c r="BF13" t="inlineStr">
-        <is>
-          <t>6.61</t>
-        </is>
-      </c>
-      <c r="BG13" t="inlineStr">
-        <is>
-          <t>-115.05</t>
-        </is>
-      </c>
-      <c r="BH13" t="inlineStr">
-        <is>
-          <t>2025/11/26</t>
-        </is>
-      </c>
-      <c r="BI13" t="inlineStr">
-        <is>
-          <t>84393600.5937931</t>
-        </is>
-      </c>
-      <c r="BJ13" t="inlineStr">
-        <is>
-          <t>17527989.0</t>
-        </is>
-      </c>
-      <c r="BK13" t="n">
-        <v>14013974.4</v>
-      </c>
-      <c r="BL13" t="inlineStr">
-        <is>
-          <t>14909019.4</t>
-        </is>
-      </c>
-      <c r="BM13" t="n">
-        <v>27619678.84</v>
-      </c>
-      <c r="BN13" t="inlineStr">
-        <is>
-          <t>-895045</t>
-        </is>
-      </c>
-      <c r="BO13" t="inlineStr">
-        <is>
-          <t>-1851052.204918465</t>
-        </is>
-      </c>
-      <c r="BP13" t="inlineStr">
-        <is>
-          <t>-1267841.888641076</t>
-        </is>
-      </c>
-      <c r="BQ13" t="inlineStr">
-        <is>
-          <t>17527989.0</t>
-        </is>
-      </c>
-      <c r="BR13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS13" t="inlineStr">
-        <is>
-          <t>160.0</t>
-        </is>
-      </c>
-      <c r="BT13" t="inlineStr">
-        <is>
-          <t>2025/07/24</t>
-        </is>
-      </c>
-      <c r="BU13" t="inlineStr">
-        <is>
-          <t>-5.62</t>
-        </is>
-      </c>
-      <c r="BV13" t="inlineStr">
-        <is>
-          <t>敦陽科</t>
-        </is>
-      </c>
-      <c r="BW13" t="inlineStr">
-        <is>
-          <t>敦陽科</t>
-        </is>
-      </c>
-      <c r="BX13" t="inlineStr">
-        <is>
-          <t>資訊服務業</t>
-        </is>
-      </c>
-      <c r="BY13" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BZ13" t="inlineStr">
-        <is>
-          <t>0.68</t>
-        </is>
-      </c>
-      <c r="CA13" t="inlineStr">
-        <is>
-          <t>-12.58214103619475</t>
-        </is>
-      </c>
-      <c r="CB13" t="inlineStr">
-        <is>
-          <t>1.043189390647018</t>
-        </is>
-      </c>
-      <c r="CC13" t="inlineStr">
-        <is>
-          <t>13.35381850712726</t>
-        </is>
-      </c>
-      <c r="CD13" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CE13" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CF13" t="inlineStr">
-        <is>
-          <t>4.90</t>
-        </is>
-      </c>
-      <c r="CG13" t="inlineStr">
-        <is>
-          <t>4.98</t>
-        </is>
-      </c>
-      <c r="CH13" t="inlineStr">
-        <is>
-          <t>18.41</t>
-        </is>
-      </c>
-      <c r="CI13" t="inlineStr">
-        <is>
-          <t>18.84</t>
-        </is>
-      </c>
-      <c r="CJ13" t="inlineStr">
-        <is>
-          <t>24.79%</t>
-        </is>
-      </c>
-      <c r="CK13" t="inlineStr">
-        <is>
-          <t>12.14%</t>
-        </is>
-      </c>
-      <c r="CL13" t="inlineStr">
-        <is>
-          <t>27.49</t>
-        </is>
-      </c>
-      <c r="CM13" t="inlineStr">
-        <is>
-          <t>15848</t>
-        </is>
-      </c>
-      <c r="CN13" t="inlineStr">
-        <is>
-          <t>諮詢與維修服務31.76%、電腦軟體19.44%、網路產品17.90%、儲存設備16.51%、工作站及伺服器主機10.52%、電腦周邊產品3.19%、個人電腦(PC)0.57%、其他0.11% (2024年)</t>
-        </is>
-      </c>
-      <c r="CO13" t="inlineStr">
-        <is>
-          <t>敦陽科-資訊服務業-上市</t>
-        </is>
-      </c>
-      <c r="CP13" t="inlineStr">
-        <is>
-          <t>資訊服務業右上上市</t>
-        </is>
-      </c>
-      <c r="CQ13" t="inlineStr">
-        <is>
-          <t>152.0</t>
-        </is>
-      </c>
-      <c r="CR13" t="inlineStr">
+      <c r="CT13" t="inlineStr">
         <is>
           <t>152.5</t>
-        </is>
-      </c>
-      <c r="CS13" t="inlineStr">
-        <is>
-          <t>151.0</t>
-        </is>
-      </c>
-      <c r="CT13" t="inlineStr">
-        <is>
-          <t>151.0</t>
         </is>
       </c>
       <c r="CU13" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>74.286</t>
+          <t>115.634</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6817,17 +6817,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-24.64</t>
+          <t>-6.00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-10.85</t>
+          <t>-11.44</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -6967,17 +6967,17 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -6988,38 +6988,38 @@
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>141</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>90.48</t>
         </is>
       </c>
       <c r="AU14" t="n">
-        <v>0.66</v>
+        <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.63</v>
+        <v>0.68</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -7028,26 +7028,26 @@
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>150.05</v>
+        <v>149.98</v>
       </c>
       <c r="BA14" t="n">
-        <v>153.1</v>
+        <v>152.82</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>159.8</t>
+          <t>159.57</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>56.43</t>
+          <t>58.36</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>-0.5</v>
+        <v>-0.41</v>
       </c>
       <c r="BE14" t="n">
-        <v>-1.14</v>
+        <v>-0.99</v>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-117.24</t>
+          <t>-115.05</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7066,43 +7066,43 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>84393600.5937931</t>
+          <t>84320789.57231405</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>11220276.0</t>
+          <t>17527989.0</t>
         </is>
       </c>
       <c r="BK14" t="n">
-        <v>12367937.2</v>
+        <v>14013974.4</v>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>16412663.9</t>
+          <t>14909019.4</t>
         </is>
       </c>
       <c r="BM14" t="n">
-        <v>27929263.46</v>
+        <v>27619678.84</v>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>-4044726</t>
+          <t>-895045</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>-1957090.444241627</t>
+          <t>-1851052.204918465</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>-1686499.540288348</t>
+          <t>-1267841.888641076</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>11220276.0</t>
+          <t>17527989.0</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>-5.00</t>
+          <t>-5.62</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
@@ -7177,12 +7177,12 @@
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="CI14" t="inlineStr">
         <is>
-          <t>18.84</t>
+          <t>18.96</t>
         </is>
       </c>
       <c r="CJ14" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>27.49</t>
+          <t>27.78</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
         <is>
-          <t>15848</t>
+          <t>15954</t>
         </is>
       </c>
       <c r="CN14" t="inlineStr">
@@ -7232,22 +7232,22 @@
       </c>
       <c r="CQ14" t="inlineStr">
         <is>
-          <t>151.5</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="CR14" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="CT14" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="CU14" t="inlineStr">
@@ -7279,12 +7279,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>108.553</t>
+          <t>74.286</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7304,17 +7304,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-16.43</t>
+          <t>-24.64</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -7454,17 +7454,17 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -7475,12 +7475,12 @@
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>141</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -7490,51 +7490,51 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>81.82</t>
+          <t>87.88</t>
         </is>
       </c>
       <c r="AU15" t="n">
-        <v>0.73</v>
+        <v>0.66</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.53</v>
+        <v>0.63</v>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>150.9</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>150.1</v>
+        <v>150.05</v>
       </c>
       <c r="BA15" t="n">
-        <v>153.38</v>
+        <v>153.1</v>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>159.99</t>
+          <t>159.8</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>46.45</t>
+          <t>56.43</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>-0.7</v>
+        <v>-0.5</v>
       </c>
       <c r="BE15" t="n">
-        <v>-1.3</v>
+        <v>-1.14</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-119.67</t>
+          <t>-117.24</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7553,43 +7553,43 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>84393600.5937931</t>
+          <t>84320789.57231405</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>16418900.0</t>
+          <t>11220276.0</t>
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>14442770</v>
+        <v>12367937.2</v>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>17281594.0</t>
+          <t>16412663.9</t>
         </is>
       </c>
       <c r="BM15" t="n">
-        <v>28315265.6</v>
+        <v>27929263.46</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>-2838824</t>
+          <t>-4044726</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>-2006288.790414951</t>
+          <t>-1957090.444241627</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>-1548523.380488437</t>
+          <t>-1686499.540288348</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>16418900.0</t>
+          <t>11220276.0</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -7654,7 +7654,7 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
@@ -7669,7 +7669,7 @@
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="CI15" t="inlineStr">
         <is>
-          <t>18.84</t>
+          <t>18.96</t>
         </is>
       </c>
       <c r="CJ15" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>27.49</t>
+          <t>27.78</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
         <is>
-          <t>15848</t>
+          <t>15954</t>
         </is>
       </c>
       <c r="CN15" t="inlineStr">
@@ -7719,7 +7719,7 @@
       </c>
       <c r="CQ15" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>151.5</t>
         </is>
       </c>
       <c r="CR15" t="inlineStr">
@@ -7729,7 +7729,7 @@
       </c>
       <c r="CS15" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="CT15" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>87.718</t>
+          <t>108.553</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7791,17 +7791,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-5.13</t>
+          <t>-16.43</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-12.32</t>
+          <t>-10.85</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -7941,17 +7941,17 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -7962,66 +7962,66 @@
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>141</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>63.64</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>78.79</t>
+          <t>81.82</t>
         </is>
       </c>
       <c r="AU16" t="n">
-        <v>-0.66</v>
+        <v>0.73</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.25</v>
+        <v>0.53</v>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>150.9</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>150.12</v>
+        <v>150.1</v>
       </c>
       <c r="BA16" t="n">
-        <v>153.68</v>
+        <v>153.38</v>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>160.21</t>
+          <t>159.99</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>35.15</t>
+          <t>46.45</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.7</v>
       </c>
       <c r="BE16" t="n">
-        <v>-1.45</v>
+        <v>-1.3</v>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-121.96</t>
+          <t>-119.67</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8040,43 +8040,43 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>84393600.5937931</t>
+          <t>84320789.57231405</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>13144876.0</t>
+          <t>16418900.0</t>
         </is>
       </c>
       <c r="BK16" t="n">
-        <v>15485293.8</v>
+        <v>14442770</v>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>16322609.4</t>
+          <t>17281594.0</t>
         </is>
       </c>
       <c r="BM16" t="n">
-        <v>28961167.86</v>
+        <v>28315265.6</v>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>-837315</t>
+          <t>-2838824</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>-2089518.864947044</t>
+          <t>-2006288.790414951</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>-1853105.602899689</t>
+          <t>-1548523.380488437</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>13144876.0</t>
+          <t>16418900.0</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>-6.56</t>
+          <t>-5.00</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
@@ -8151,12 +8151,12 @@
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="CI16" t="inlineStr">
         <is>
-          <t>18.84</t>
+          <t>18.96</t>
         </is>
       </c>
       <c r="CJ16" t="inlineStr">
@@ -8181,12 +8181,12 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>27.49</t>
+          <t>27.78</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
         <is>
-          <t>15848</t>
+          <t>15954</t>
         </is>
       </c>
       <c r="CN16" t="inlineStr">
@@ -8206,22 +8206,22 @@
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="CR16" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="CT16" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="CU16" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>77.954</t>
+          <t>87.718</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8278,17 +8278,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-5.73</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-11.73</t>
+          <t>-12.32</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -8428,17 +8428,17 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -8449,66 +8449,66 @@
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>141</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>81.82</t>
+          <t>63.64</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>78.79</t>
         </is>
       </c>
       <c r="AU17" t="n">
-        <v>0.13</v>
+        <v>-0.66</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.08</v>
+        <v>0.25</v>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>150.3</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>150.18</v>
+        <v>150.12</v>
       </c>
       <c r="BA17" t="n">
-        <v>154.11</v>
+        <v>153.68</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>160.5</t>
+          <t>160.21</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>37.59</t>
+          <t>35.15</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>-0.98</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="BE17" t="n">
-        <v>-1.58</v>
+        <v>-1.45</v>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-123.89</t>
+          <t>-121.96</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8527,43 +8527,43 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>84393600.5937931</t>
+          <t>84320789.57231405</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>11757831.0</t>
+          <t>13144876.0</t>
         </is>
       </c>
       <c r="BK17" t="n">
-        <v>15466792.6</v>
+        <v>15485293.8</v>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>16407454.4</t>
+          <t>16322609.4</t>
         </is>
       </c>
       <c r="BM17" t="n">
-        <v>29983507.82</v>
+        <v>28961167.86</v>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>-940661</t>
+          <t>-837315</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>-2132503.0944102</t>
+          <t>-2089518.864947044</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>-1871252.434812207</t>
+          <t>-1853105.602899689</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>11757831.0</t>
+          <t>13144876.0</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-6.56</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -8608,7 +8608,7 @@
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
@@ -8638,12 +8638,12 @@
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="CI17" t="inlineStr">
         <is>
-          <t>18.84</t>
+          <t>18.96</t>
         </is>
       </c>
       <c r="CJ17" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>27.49</t>
+          <t>27.78</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
         <is>
-          <t>15848</t>
+          <t>15954</t>
         </is>
       </c>
       <c r="CN17" t="inlineStr">
@@ -8693,22 +8693,22 @@
       </c>
       <c r="CQ17" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="CR17" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CT17" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="CU17" t="inlineStr">
@@ -8730,7 +8730,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8745,7 +8745,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>61.276</t>
+          <t>77.954</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8765,17 +8765,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-3.60</t>
+          <t>-5.73</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-11.44</t>
+          <t>-11.73</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -8915,17 +8915,17 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -8936,66 +8936,66 @@
       <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>141</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
+          <t>81.82</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr">
+        <is>
           <t>90.91</t>
         </is>
       </c>
-      <c r="AT18" t="inlineStr">
-        <is>
-          <t>93.27</t>
-        </is>
-      </c>
       <c r="AU18" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.13</v>
       </c>
       <c r="AV18" t="n">
-        <v>-0.33</v>
+        <v>0.08</v>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>-2.8</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>149.6</t>
+          <t>150.3</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>150.1</v>
+        <v>150.18</v>
       </c>
       <c r="BA18" t="n">
-        <v>154.42</v>
+        <v>154.11</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>160.79</t>
+          <t>160.5</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>34.62</t>
+          <t>37.59</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>-1.13</v>
+        <v>-0.98</v>
       </c>
       <c r="BE18" t="n">
-        <v>-1.73</v>
+        <v>-1.58</v>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-126.13</t>
+          <t>-123.89</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9014,43 +9014,43 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>84393600.5937931</t>
+          <t>84320789.57231405</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>9297803.0</t>
+          <t>11757831.0</t>
         </is>
       </c>
       <c r="BK18" t="n">
-        <v>15804064.4</v>
+        <v>15466792.6</v>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>16394095.4</t>
+          <t>16407454.4</t>
         </is>
       </c>
       <c r="BM18" t="n">
-        <v>31853468.84</v>
+        <v>29983507.82</v>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>-590031</t>
+          <t>-940661</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>-2180003.214337108</t>
+          <t>-2132503.0944102</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>-1681734.072015364</t>
+          <t>-1871252.434812207</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>9297803.0</t>
+          <t>11757831.0</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>-5.62</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -9095,7 +9095,7 @@
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -9115,7 +9115,7 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
@@ -9125,12 +9125,12 @@
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="CI18" t="inlineStr">
         <is>
-          <t>18.84</t>
+          <t>18.96</t>
         </is>
       </c>
       <c r="CJ18" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>27.49</t>
+          <t>27.78</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
         <is>
-          <t>15848</t>
+          <t>15954</t>
         </is>
       </c>
       <c r="CN18" t="inlineStr">
@@ -9180,22 +9180,22 @@
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="CR18" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="CT18" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="CU18" t="inlineStr">
@@ -9227,12 +9227,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>142.317</t>
+          <t>61.276</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>151.5</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -9252,17 +9252,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>17.39</t>
+          <t>-3.60</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -9327,7 +9327,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-11.14</t>
+          <t>-11.44</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -9402,17 +9402,17 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -9423,66 +9423,66 @@
       <c r="AP19" t="inlineStr"/>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>141</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>81.48</t>
+          <t>93.27</t>
         </is>
       </c>
       <c r="AU19" t="n">
-        <v>1.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AV19" t="n">
-        <v>-0.9</v>
+        <v>-0.33</v>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-2.8</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>148.6</t>
+          <t>149.6</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>149.95</v>
+        <v>150.1</v>
       </c>
       <c r="BA19" t="n">
-        <v>154.81</v>
+        <v>154.42</v>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>161.12</t>
+          <t>160.79</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>28.20</t>
+          <t>34.62</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>-1.35</v>
+        <v>-1.13</v>
       </c>
       <c r="BE19" t="n">
-        <v>-1.88</v>
+        <v>-1.73</v>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-128.39</t>
+          <t>-126.13</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9501,43 +9501,43 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>84393600.5937931</t>
+          <t>84320789.57231405</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>21594440.0</t>
+          <t>9297803.0</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>20457390.6</v>
+        <v>15804064.4</v>
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>17426298.0</t>
+          <t>16394095.4</t>
         </is>
       </c>
       <c r="BM19" t="n">
-        <v>32539769.02</v>
+        <v>31853468.84</v>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>3031092</t>
+          <t>-590031</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>-2270597.603850152</t>
+          <t>-2180003.214337108</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>-1087357.194019325</t>
+          <t>-1681734.072015364</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>21594440.0</t>
+          <t>9297803.0</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-5.62</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -9582,7 +9582,7 @@
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -9612,12 +9612,12 @@
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="CI19" t="inlineStr">
         <is>
-          <t>18.84</t>
+          <t>18.96</t>
         </is>
       </c>
       <c r="CJ19" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>27.49</t>
+          <t>27.78</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
         <is>
-          <t>15848</t>
+          <t>15954</t>
         </is>
       </c>
       <c r="CN19" t="inlineStr">
@@ -9667,22 +9667,22 @@
       </c>
       <c r="CQ19" t="inlineStr">
         <is>
+          <t>153.0</t>
+        </is>
+      </c>
+      <c r="CR19" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
+      <c r="CS19" t="inlineStr">
+        <is>
           <t>151.0</t>
         </is>
       </c>
-      <c r="CR19" t="inlineStr">
-        <is>
-          <t>152.5</t>
-        </is>
-      </c>
-      <c r="CS19" t="inlineStr">
+      <c r="CT19" t="inlineStr">
         <is>
           <t>151.0</t>
-        </is>
-      </c>
-      <c r="CT19" t="inlineStr">
-        <is>
-          <t>151.5</t>
         </is>
       </c>
       <c r="CU19" t="inlineStr">
@@ -9714,12 +9714,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>495.02</t>
+          <t>265.555</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9729,7 +9729,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -9744,12 +9744,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>21.23</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-14.63</t>
+          <t>-14.31</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -9889,17 +9889,17 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -9910,66 +9910,66 @@
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>266</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>52.38</t>
+          <t>38.89</t>
         </is>
       </c>
       <c r="AU20" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.45</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.08</v>
+        <v>0.01</v>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>-4.54</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>52.94</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>52.96</v>
+        <v>52.94</v>
       </c>
       <c r="BA20" t="n">
-        <v>53.99</v>
+        <v>53.88</v>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>56.53</t>
+          <t>56.44</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>34.36</t>
+          <t>29.03</t>
         </is>
       </c>
       <c r="BD20" t="n">
         <v>-0.24</v>
       </c>
       <c r="BE20" t="n">
-        <v>-0.37</v>
+        <v>-0.34</v>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-105.00</t>
+          <t>-104.66</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -9988,43 +9988,43 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>321111602.0667614</t>
+          <t>320685940.6042553</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
-          <t>26109889.0</t>
+          <t>14013514.0</t>
         </is>
       </c>
       <c r="BK20" t="n">
-        <v>15679921.4</v>
+        <v>16031674.6</v>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>12700588.3</t>
+          <t>13224673.2</t>
         </is>
       </c>
       <c r="BM20" t="n">
-        <v>21036816.08</v>
+        <v>19153862.4</v>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>2979333</t>
+          <t>2807001</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>-970088.2951638207</t>
+          <t>-714450.7190633711</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>900415.2365907561</t>
+          <t>691555.9494891018</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>26109889.0</t>
+          <t>14013514.0</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>-10.10</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -10069,7 +10069,7 @@
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -10089,7 +10089,7 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
@@ -10099,12 +10099,12 @@
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="CI20" t="inlineStr">
         <is>
-          <t>16.51</t>
+          <t>16.57</t>
         </is>
       </c>
       <c r="CJ20" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>27.49</t>
+          <t>27.78</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5270</t>
         </is>
       </c>
       <c r="CN20" t="inlineStr">
@@ -10154,22 +10154,22 @@
       </c>
       <c r="CQ20" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="CR20" t="inlineStr">
         <is>
-          <t>53.9</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CS20" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CT20" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CU20" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>407.996</t>
+          <t>495.02</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -10226,17 +10226,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>17.98</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -10301,7 +10301,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-12.68</t>
+          <t>-14.63</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -10376,17 +10376,17 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -10397,66 +10397,66 @@
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>266</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>52.38</t>
         </is>
       </c>
       <c r="AU21" t="n">
-        <v>1.28</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AV21" t="n">
         <v>0.08</v>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>-4.39</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>53.02</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>52.98</v>
+        <v>52.96</v>
       </c>
       <c r="BA21" t="n">
-        <v>54.12</v>
+        <v>53.99</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>56.61</t>
+          <t>56.53</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>46.13</t>
+          <t>34.36</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>-0.22</v>
+        <v>-0.24</v>
       </c>
       <c r="BE21" t="n">
-        <v>-0.4</v>
+        <v>-0.37</v>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-105.43</t>
+          <t>-105.00</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -10475,43 +10475,43 @@
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>321111602.0667614</t>
+          <t>320685940.6042553</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
         <is>
-          <t>21876866.0</t>
+          <t>26109889.0</t>
         </is>
       </c>
       <c r="BK21" t="n">
-        <v>12947867.4</v>
+        <v>15679921.4</v>
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>10974866.2</t>
+          <t>12700588.3</t>
         </is>
       </c>
       <c r="BM21" t="n">
-        <v>21858432.98</v>
+        <v>21036816.08</v>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>1973001</t>
+          <t>2979333</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>-1310179.846391926</t>
+          <t>-970088.2951638207</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>-129412.2188565508</t>
+          <t>900415.2365907561</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>21876866.0</t>
+          <t>26109889.0</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>-8.05</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -10556,7 +10556,7 @@
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -10576,7 +10576,7 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="CI21" t="inlineStr">
         <is>
-          <t>16.51</t>
+          <t>16.57</t>
         </is>
       </c>
       <c r="CJ21" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>27.49</t>
+          <t>27.78</t>
         </is>
       </c>
       <c r="CM21" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5270</t>
         </is>
       </c>
       <c r="CN21" t="inlineStr">
@@ -10641,22 +10641,22 @@
       </c>
       <c r="CQ21" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="CR21" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.9</t>
         </is>
       </c>
       <c r="CS21" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CT21" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CU21" t="inlineStr">
@@ -10678,7 +10678,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -10688,12 +10688,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>157.66</t>
+          <t>407.996</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -10713,17 +10713,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>17.98</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-13.82</t>
+          <t>-12.68</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -10863,12 +10863,12 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
@@ -10884,66 +10884,66 @@
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>266</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>52.38</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AU22" t="n">
-        <v>0.23</v>
+        <v>1.28</v>
       </c>
       <c r="AV22" t="n">
-        <v>-0.05</v>
+        <v>0.08</v>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>-2.4</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>-4.37</t>
+          <t>-4.39</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>52.88</t>
+          <t>53.02</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>52.9</v>
+        <v>52.98</v>
       </c>
       <c r="BA22" t="n">
-        <v>54.21</v>
+        <v>54.12</v>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>56.68</t>
+          <t>56.61</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>32.59</t>
+          <t>46.13</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>-0.3</v>
+        <v>-0.22</v>
       </c>
       <c r="BE22" t="n">
-        <v>-0.45</v>
+        <v>-0.4</v>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-106.06</t>
+          <t>-105.43</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -10962,43 +10962,43 @@
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>321111602.0667614</t>
+          <t>320685940.6042553</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
         <is>
-          <t>8327433.0</t>
+          <t>21876866.0</t>
         </is>
       </c>
       <c r="BK22" t="n">
-        <v>9620035.4</v>
+        <v>12947867.4</v>
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>10202853.7</t>
+          <t>10974866.2</t>
         </is>
       </c>
       <c r="BM22" t="n">
-        <v>22056560.66</v>
+        <v>21858432.98</v>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>-582818</t>
+          <t>1973001</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>-1524864.869580176</t>
+          <t>-1310179.846391926</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>-1142434.254536396</t>
+          <t>-129412.2188565508</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>8327433.0</t>
+          <t>21876866.0</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>-9.25</t>
+          <t>-8.05</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -11043,7 +11043,7 @@
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -11063,7 +11063,7 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
@@ -11073,12 +11073,12 @@
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="CI22" t="inlineStr">
         <is>
-          <t>16.51</t>
+          <t>16.57</t>
         </is>
       </c>
       <c r="CJ22" t="inlineStr">
@@ -11103,12 +11103,12 @@
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>27.49</t>
+          <t>27.78</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5270</t>
         </is>
       </c>
       <c r="CN22" t="inlineStr">
@@ -11128,22 +11128,22 @@
       </c>
       <c r="CQ22" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CR22" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CT22" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="CU22" t="inlineStr">
@@ -11165,7 +11165,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -11175,12 +11175,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>187.396</t>
+          <t>157.66</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-11.07</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-14.15</t>
+          <t>-13.82</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -11350,17 +11350,17 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -11371,66 +11371,66 @@
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>266</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>52.38</t>
         </is>
       </c>
       <c r="AU23" t="n">
-        <v>-0.26</v>
+        <v>0.23</v>
       </c>
       <c r="AV23" t="n">
-        <v>0.1</v>
+        <v>-0.05</v>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>-4.36</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>52.94</t>
+          <t>52.88</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>52.89</v>
+        <v>52.9</v>
       </c>
       <c r="BA23" t="n">
-        <v>54.3</v>
+        <v>54.21</v>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>56.78</t>
+          <t>56.68</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>32.59</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>-0.33</v>
+        <v>-0.3</v>
       </c>
       <c r="BE23" t="n">
-        <v>-0.48</v>
+        <v>-0.45</v>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-106.55</t>
+          <t>-106.06</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -11449,43 +11449,43 @@
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>321111602.0667614</t>
+          <t>320685940.6042553</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
         <is>
-          <t>9830671.0</t>
+          <t>8327433.0</t>
         </is>
       </c>
       <c r="BK23" t="n">
-        <v>9505074.6</v>
+        <v>9620035.4</v>
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>10688450.6</t>
+          <t>10202853.7</t>
         </is>
       </c>
       <c r="BM23" t="n">
-        <v>22594895.62</v>
+        <v>22056560.66</v>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>-1183376</t>
+          <t>-582818</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>-1594397.708679045</t>
+          <t>-1524864.869580176</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>-1097082.403559875</t>
+          <t>-1142434.254536396</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>9830671.0</t>
+          <t>8327433.0</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>-9.59</t>
+          <t>-9.25</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -11530,7 +11530,7 @@
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -11550,7 +11550,7 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
@@ -11560,12 +11560,12 @@
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="CI23" t="inlineStr">
         <is>
-          <t>16.51</t>
+          <t>16.57</t>
         </is>
       </c>
       <c r="CJ23" t="inlineStr">
@@ -11590,12 +11590,12 @@
       </c>
       <c r="CL23" t="inlineStr">
         <is>
-          <t>27.49</t>
+          <t>27.78</t>
         </is>
       </c>
       <c r="CM23" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5270</t>
         </is>
       </c>
       <c r="CN23" t="inlineStr">
@@ -11615,22 +11615,22 @@
       </c>
       <c r="CQ23" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CR23" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CT23" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CU23" t="inlineStr">
@@ -11662,12 +11662,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>230.726</t>
+          <t>187.396</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -11687,17 +11687,17 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>-11.07</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -11762,7 +11762,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>-13.82</t>
+          <t>-14.15</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -11837,17 +11837,17 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -11858,266 +11858,266 @@
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>266</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>47.62</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AU24" t="n">
-        <v>-0.19</v>
+        <v>-0.26</v>
       </c>
       <c r="AV24" t="n">
-        <v>0.43</v>
+        <v>0.1</v>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>-2.8</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-4.36</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
+          <t>52.94</t>
+        </is>
+      </c>
+      <c r="AZ24" t="n">
+        <v>52.89</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="BB24" t="inlineStr">
+        <is>
+          <t>56.78</t>
+        </is>
+      </c>
+      <c r="BC24" t="inlineStr">
+        <is>
+          <t>30.77</t>
+        </is>
+      </c>
+      <c r="BD24" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="BF24" t="inlineStr">
+        <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="BG24" t="inlineStr">
+        <is>
+          <t>-106.55</t>
+        </is>
+      </c>
+      <c r="BH24" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="BI24" t="inlineStr">
+        <is>
+          <t>320685940.6042553</t>
+        </is>
+      </c>
+      <c r="BJ24" t="inlineStr">
+        <is>
+          <t>9830671.0</t>
+        </is>
+      </c>
+      <c r="BK24" t="n">
+        <v>9505074.6</v>
+      </c>
+      <c r="BL24" t="inlineStr">
+        <is>
+          <t>10688450.6</t>
+        </is>
+      </c>
+      <c r="BM24" t="n">
+        <v>22594895.62</v>
+      </c>
+      <c r="BN24" t="inlineStr">
+        <is>
+          <t>-1183376</t>
+        </is>
+      </c>
+      <c r="BO24" t="inlineStr">
+        <is>
+          <t>-1594397.708679045</t>
+        </is>
+      </c>
+      <c r="BP24" t="inlineStr">
+        <is>
+          <t>-1097082.403559875</t>
+        </is>
+      </c>
+      <c r="BQ24" t="inlineStr">
+        <is>
+          <t>9830671.0</t>
+        </is>
+      </c>
+      <c r="BR24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS24" t="inlineStr">
+        <is>
+          <t>58.4</t>
+        </is>
+      </c>
+      <c r="BT24" t="inlineStr">
+        <is>
+          <t>2025/08/13</t>
+        </is>
+      </c>
+      <c r="BU24" t="inlineStr">
+        <is>
+          <t>-9.59</t>
+        </is>
+      </c>
+      <c r="BV24" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BW24" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BX24" t="inlineStr">
+        <is>
+          <t>資訊服務業</t>
+        </is>
+      </c>
+      <c r="BY24" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BZ24" t="inlineStr">
+        <is>
+          <t>0.89</t>
+        </is>
+      </c>
+      <c r="CA24" t="inlineStr">
+        <is>
+          <t>22.56022604840866</t>
+        </is>
+      </c>
+      <c r="CB24" t="inlineStr">
+        <is>
+          <t>4.850028625915454</t>
+        </is>
+      </c>
+      <c r="CC24" t="inlineStr">
+        <is>
+          <t>7.335967839135664</t>
+        </is>
+      </c>
+      <c r="CD24" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE24" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CF24" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="CG24" t="inlineStr">
+        <is>
+          <t>4.93</t>
+        </is>
+      </c>
+      <c r="CH24" t="inlineStr">
+        <is>
+          <t>18.50</t>
+        </is>
+      </c>
+      <c r="CI24" t="inlineStr">
+        <is>
+          <t>16.57</t>
+        </is>
+      </c>
+      <c r="CJ24" t="inlineStr">
+        <is>
+          <t>25.81%</t>
+        </is>
+      </c>
+      <c r="CK24" t="inlineStr">
+        <is>
+          <t>3.37%</t>
+        </is>
+      </c>
+      <c r="CL24" t="inlineStr">
+        <is>
+          <t>27.78</t>
+        </is>
+      </c>
+      <c r="CM24" t="inlineStr">
+        <is>
+          <t>5270</t>
+        </is>
+      </c>
+      <c r="CN24" t="inlineStr">
+        <is>
+          <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CO24" t="inlineStr">
+        <is>
+          <t>凌群-資訊服務業-上市</t>
+        </is>
+      </c>
+      <c r="CP24" t="inlineStr">
+        <is>
+          <t>資訊服務業右下上市</t>
+        </is>
+      </c>
+      <c r="CQ24" t="inlineStr">
+        <is>
           <t>53.1</t>
         </is>
       </c>
-      <c r="AZ24" t="n">
-        <v>52.88</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>54.4</v>
-      </c>
-      <c r="BB24" t="inlineStr">
-        <is>
-          <t>56.87</t>
-        </is>
-      </c>
-      <c r="BC24" t="inlineStr">
-        <is>
-          <t>32.39</t>
-        </is>
-      </c>
-      <c r="BD24" t="n">
-        <v>-0.35</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>-0.52</v>
-      </c>
-      <c r="BF24" t="inlineStr">
-        <is>
-          <t>7.38</t>
-        </is>
-      </c>
-      <c r="BG24" t="inlineStr">
-        <is>
-          <t>-107.05</t>
-        </is>
-      </c>
-      <c r="BH24" t="inlineStr">
-        <is>
-          <t>2025/12/01</t>
-        </is>
-      </c>
-      <c r="BI24" t="inlineStr">
-        <is>
-          <t>321111602.0667614</t>
-        </is>
-      </c>
-      <c r="BJ24" t="inlineStr">
-        <is>
-          <t>12254748.0</t>
-        </is>
-      </c>
-      <c r="BK24" t="n">
-        <v>10417671.8</v>
-      </c>
-      <c r="BL24" t="inlineStr">
-        <is>
-          <t>10395147.6</t>
-        </is>
-      </c>
-      <c r="BM24" t="n">
-        <v>23136654.44</v>
-      </c>
-      <c r="BN24" t="inlineStr">
-        <is>
-          <t>22524</t>
-        </is>
-      </c>
-      <c r="BO24" t="inlineStr">
-        <is>
-          <t>-1684818.673246166</t>
-        </is>
-      </c>
-      <c r="BP24" t="inlineStr">
-        <is>
-          <t>-1154173.744894853</t>
-        </is>
-      </c>
-      <c r="BQ24" t="inlineStr">
-        <is>
-          <t>12254748.0</t>
-        </is>
-      </c>
-      <c r="BR24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS24" t="inlineStr">
-        <is>
-          <t>58.4</t>
-        </is>
-      </c>
-      <c r="BT24" t="inlineStr">
-        <is>
-          <t>2025/08/13</t>
-        </is>
-      </c>
-      <c r="BU24" t="inlineStr">
-        <is>
-          <t>-9.25</t>
-        </is>
-      </c>
-      <c r="BV24" t="inlineStr">
-        <is>
-          <t>凌群</t>
-        </is>
-      </c>
-      <c r="BW24" t="inlineStr">
-        <is>
-          <t>凌群</t>
-        </is>
-      </c>
-      <c r="BX24" t="inlineStr">
-        <is>
-          <t>資訊服務業</t>
-        </is>
-      </c>
-      <c r="BY24" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BZ24" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="CA24" t="inlineStr">
-        <is>
-          <t>22.56022604840866</t>
-        </is>
-      </c>
-      <c r="CB24" t="inlineStr">
-        <is>
-          <t>4.850028625915454</t>
-        </is>
-      </c>
-      <c r="CC24" t="inlineStr">
-        <is>
-          <t>7.335967839135664</t>
-        </is>
-      </c>
-      <c r="CD24" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CE24" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CF24" t="inlineStr">
-        <is>
-          <t>2.49</t>
-        </is>
-      </c>
-      <c r="CG24" t="inlineStr">
-        <is>
-          <t>4.95</t>
-        </is>
-      </c>
-      <c r="CH24" t="inlineStr">
-        <is>
-          <t>18.50</t>
-        </is>
-      </c>
-      <c r="CI24" t="inlineStr">
-        <is>
-          <t>16.51</t>
-        </is>
-      </c>
-      <c r="CJ24" t="inlineStr">
-        <is>
-          <t>25.81%</t>
-        </is>
-      </c>
-      <c r="CK24" t="inlineStr">
-        <is>
-          <t>3.37%</t>
-        </is>
-      </c>
-      <c r="CL24" t="inlineStr">
-        <is>
-          <t>27.49</t>
-        </is>
-      </c>
-      <c r="CM24" t="inlineStr">
-        <is>
-          <t>5250</t>
-        </is>
-      </c>
-      <c r="CN24" t="inlineStr">
-        <is>
-          <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
-        </is>
-      </c>
-      <c r="CO24" t="inlineStr">
-        <is>
-          <t>凌群-資訊服務業-上市</t>
-        </is>
-      </c>
-      <c r="CP24" t="inlineStr">
-        <is>
-          <t>資訊服務業右下上市</t>
-        </is>
-      </c>
-      <c r="CQ24" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
       <c r="CR24" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CS24" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CT24" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CU24" t="inlineStr">
@@ -12149,12 +12149,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>236.727</t>
+          <t>230.726</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -12174,17 +12174,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -12249,7 +12249,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>-14.47</t>
+          <t>-13.82</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -12324,12 +12324,12 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
@@ -12345,266 +12345,266 @@
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>266</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>54.76</t>
+          <t>47.62</t>
         </is>
       </c>
       <c r="AU25" t="n">
-        <v>-0.75</v>
+        <v>-0.19</v>
       </c>
       <c r="AV25" t="n">
-        <v>0.28</v>
+        <v>0.43</v>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-2.8</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
+          <t>53.1</t>
+        </is>
+      </c>
+      <c r="AZ25" t="n">
+        <v>52.88</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="BB25" t="inlineStr">
+        <is>
+          <t>56.87</t>
+        </is>
+      </c>
+      <c r="BC25" t="inlineStr">
+        <is>
+          <t>32.39</t>
+        </is>
+      </c>
+      <c r="BD25" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="BF25" t="inlineStr">
+        <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="BG25" t="inlineStr">
+        <is>
+          <t>-107.05</t>
+        </is>
+      </c>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="BI25" t="inlineStr">
+        <is>
+          <t>320685940.6042553</t>
+        </is>
+      </c>
+      <c r="BJ25" t="inlineStr">
+        <is>
+          <t>12254748.0</t>
+        </is>
+      </c>
+      <c r="BK25" t="n">
+        <v>10417671.8</v>
+      </c>
+      <c r="BL25" t="inlineStr">
+        <is>
+          <t>10395147.6</t>
+        </is>
+      </c>
+      <c r="BM25" t="n">
+        <v>23136654.44</v>
+      </c>
+      <c r="BN25" t="inlineStr">
+        <is>
+          <t>22524</t>
+        </is>
+      </c>
+      <c r="BO25" t="inlineStr">
+        <is>
+          <t>-1684818.673246166</t>
+        </is>
+      </c>
+      <c r="BP25" t="inlineStr">
+        <is>
+          <t>-1154173.744894853</t>
+        </is>
+      </c>
+      <c r="BQ25" t="inlineStr">
+        <is>
+          <t>12254748.0</t>
+        </is>
+      </c>
+      <c r="BR25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS25" t="inlineStr">
+        <is>
+          <t>58.4</t>
+        </is>
+      </c>
+      <c r="BT25" t="inlineStr">
+        <is>
+          <t>2025/08/13</t>
+        </is>
+      </c>
+      <c r="BU25" t="inlineStr">
+        <is>
+          <t>-9.25</t>
+        </is>
+      </c>
+      <c r="BV25" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BW25" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BX25" t="inlineStr">
+        <is>
+          <t>資訊服務業</t>
+        </is>
+      </c>
+      <c r="BY25" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BZ25" t="inlineStr">
+        <is>
+          <t>0.89</t>
+        </is>
+      </c>
+      <c r="CA25" t="inlineStr">
+        <is>
+          <t>22.56022604840866</t>
+        </is>
+      </c>
+      <c r="CB25" t="inlineStr">
+        <is>
+          <t>4.850028625915454</t>
+        </is>
+      </c>
+      <c r="CC25" t="inlineStr">
+        <is>
+          <t>7.335967839135664</t>
+        </is>
+      </c>
+      <c r="CD25" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE25" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CF25" t="inlineStr">
+        <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="CG25" t="inlineStr">
+        <is>
+          <t>4.93</t>
+        </is>
+      </c>
+      <c r="CH25" t="inlineStr">
+        <is>
+          <t>18.50</t>
+        </is>
+      </c>
+      <c r="CI25" t="inlineStr">
+        <is>
+          <t>16.57</t>
+        </is>
+      </c>
+      <c r="CJ25" t="inlineStr">
+        <is>
+          <t>25.81%</t>
+        </is>
+      </c>
+      <c r="CK25" t="inlineStr">
+        <is>
+          <t>3.37%</t>
+        </is>
+      </c>
+      <c r="CL25" t="inlineStr">
+        <is>
+          <t>27.78</t>
+        </is>
+      </c>
+      <c r="CM25" t="inlineStr">
+        <is>
+          <t>5270</t>
+        </is>
+      </c>
+      <c r="CN25" t="inlineStr">
+        <is>
+          <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CO25" t="inlineStr">
+        <is>
+          <t>凌群-資訊服務業-上市</t>
+        </is>
+      </c>
+      <c r="CP25" t="inlineStr">
+        <is>
+          <t>資訊服務業右下上市</t>
+        </is>
+      </c>
+      <c r="CQ25" t="inlineStr">
+        <is>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="CR25" t="inlineStr">
+        <is>
+          <t>53.5</t>
+        </is>
+      </c>
+      <c r="CS25" t="inlineStr">
+        <is>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="CT25" t="inlineStr">
+        <is>
           <t>53.0</t>
-        </is>
-      </c>
-      <c r="AZ25" t="n">
-        <v>52.85</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>54.51</v>
-      </c>
-      <c r="BB25" t="inlineStr">
-        <is>
-          <t>56.97</t>
-        </is>
-      </c>
-      <c r="BC25" t="inlineStr">
-        <is>
-          <t>30.81</t>
-        </is>
-      </c>
-      <c r="BD25" t="n">
-        <v>-0.39</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>-0.5600000000000001</v>
-      </c>
-      <c r="BF25" t="inlineStr">
-        <is>
-          <t>7.38</t>
-        </is>
-      </c>
-      <c r="BG25" t="inlineStr">
-        <is>
-          <t>-107.62</t>
-        </is>
-      </c>
-      <c r="BH25" t="inlineStr">
-        <is>
-          <t>2025/12/01</t>
-        </is>
-      </c>
-      <c r="BI25" t="inlineStr">
-        <is>
-          <t>321111602.0667614</t>
-        </is>
-      </c>
-      <c r="BJ25" t="inlineStr">
-        <is>
-          <t>12449619.0</t>
-        </is>
-      </c>
-      <c r="BK25" t="n">
-        <v>9721255.199999999</v>
-      </c>
-      <c r="BL25" t="inlineStr">
-        <is>
-          <t>10056766.1</t>
-        </is>
-      </c>
-      <c r="BM25" t="n">
-        <v>23927706.04</v>
-      </c>
-      <c r="BN25" t="inlineStr">
-        <is>
-          <t>-335510</t>
-        </is>
-      </c>
-      <c r="BO25" t="inlineStr">
-        <is>
-          <t>-1781299.569310042</t>
-        </is>
-      </c>
-      <c r="BP25" t="inlineStr">
-        <is>
-          <t>-1454234.84877</t>
-        </is>
-      </c>
-      <c r="BQ25" t="inlineStr">
-        <is>
-          <t>12449619.0</t>
-        </is>
-      </c>
-      <c r="BR25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS25" t="inlineStr">
-        <is>
-          <t>58.4</t>
-        </is>
-      </c>
-      <c r="BT25" t="inlineStr">
-        <is>
-          <t>2025/08/13</t>
-        </is>
-      </c>
-      <c r="BU25" t="inlineStr">
-        <is>
-          <t>-9.93</t>
-        </is>
-      </c>
-      <c r="BV25" t="inlineStr">
-        <is>
-          <t>凌群</t>
-        </is>
-      </c>
-      <c r="BW25" t="inlineStr">
-        <is>
-          <t>凌群</t>
-        </is>
-      </c>
-      <c r="BX25" t="inlineStr">
-        <is>
-          <t>資訊服務業</t>
-        </is>
-      </c>
-      <c r="BY25" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BZ25" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="CA25" t="inlineStr">
-        <is>
-          <t>22.56022604840866</t>
-        </is>
-      </c>
-      <c r="CB25" t="inlineStr">
-        <is>
-          <t>4.850028625915454</t>
-        </is>
-      </c>
-      <c r="CC25" t="inlineStr">
-        <is>
-          <t>7.335967839135664</t>
-        </is>
-      </c>
-      <c r="CD25" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="CE25" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CF25" t="inlineStr">
-        <is>
-          <t>2.47</t>
-        </is>
-      </c>
-      <c r="CG25" t="inlineStr">
-        <is>
-          <t>4.95</t>
-        </is>
-      </c>
-      <c r="CH25" t="inlineStr">
-        <is>
-          <t>18.50</t>
-        </is>
-      </c>
-      <c r="CI25" t="inlineStr">
-        <is>
-          <t>16.51</t>
-        </is>
-      </c>
-      <c r="CJ25" t="inlineStr">
-        <is>
-          <t>25.81%</t>
-        </is>
-      </c>
-      <c r="CK25" t="inlineStr">
-        <is>
-          <t>3.37%</t>
-        </is>
-      </c>
-      <c r="CL25" t="inlineStr">
-        <is>
-          <t>27.49</t>
-        </is>
-      </c>
-      <c r="CM25" t="inlineStr">
-        <is>
-          <t>5250</t>
-        </is>
-      </c>
-      <c r="CN25" t="inlineStr">
-        <is>
-          <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
-        </is>
-      </c>
-      <c r="CO25" t="inlineStr">
-        <is>
-          <t>凌群-資訊服務業-上市</t>
-        </is>
-      </c>
-      <c r="CP25" t="inlineStr">
-        <is>
-          <t>資訊服務業右下上市</t>
-        </is>
-      </c>
-      <c r="CQ25" t="inlineStr">
-        <is>
-          <t>53.0</t>
-        </is>
-      </c>
-      <c r="CR25" t="inlineStr">
-        <is>
-          <t>53.1</t>
-        </is>
-      </c>
-      <c r="CS25" t="inlineStr">
-        <is>
-          <t>52.2</t>
-        </is>
-      </c>
-      <c r="CT25" t="inlineStr">
-        <is>
-          <t>52.6</t>
         </is>
       </c>
       <c r="CU25" t="inlineStr">
@@ -12636,12 +12636,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>98.917</t>
+          <t>236.727</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -12651,7 +12651,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -12661,17 +12661,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-11.03</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -12736,7 +12736,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>-13.82</t>
+          <t>-14.47</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -12811,17 +12811,17 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -12832,66 +12832,66 @@
       <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>266</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>78.57</t>
+          <t>54.76</t>
         </is>
       </c>
       <c r="AU26" t="n">
-        <v>0.15</v>
+        <v>-0.75</v>
       </c>
       <c r="AV26" t="n">
-        <v>0.17</v>
+        <v>0.28</v>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>52.92</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>52.83</v>
+        <v>52.85</v>
       </c>
       <c r="BA26" t="n">
-        <v>54.65</v>
+        <v>54.51</v>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>57.08</t>
+          <t>56.97</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>35.55</t>
+          <t>30.81</t>
         </is>
       </c>
       <c r="BD26" t="n">
         <v>-0.39</v>
       </c>
       <c r="BE26" t="n">
-        <v>-0.61</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
@@ -12900,7 +12900,7 @@
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>-108.21</t>
+          <t>-107.62</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
@@ -12910,43 +12910,43 @@
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>321111602.0667614</t>
+          <t>320685940.6042553</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
         <is>
-          <t>5237706.0</t>
+          <t>12449619.0</t>
         </is>
       </c>
       <c r="BK26" t="n">
-        <v>9001865</v>
+        <v>9721255.199999999</v>
       </c>
       <c r="BL26" t="inlineStr">
         <is>
-          <t>10118227.0</t>
+          <t>10056766.1</t>
         </is>
       </c>
       <c r="BM26" t="n">
-        <v>24497841.7</v>
+        <v>23927706.04</v>
       </c>
       <c r="BN26" t="inlineStr">
         <is>
-          <t>-1116362</t>
+          <t>-335510</t>
         </is>
       </c>
       <c r="BO26" t="inlineStr">
         <is>
-          <t>-1840765.882135504</t>
+          <t>-1781299.569310042</t>
         </is>
       </c>
       <c r="BP26" t="inlineStr">
         <is>
-          <t>-1851835.645421285</t>
+          <t>-1454234.84877</t>
         </is>
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>5237706.0</t>
+          <t>12449619.0</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
@@ -12966,7 +12966,7 @@
       </c>
       <c r="BU26" t="inlineStr">
         <is>
-          <t>-9.25</t>
+          <t>-9.93</t>
         </is>
       </c>
       <c r="BV26" t="inlineStr">
@@ -12991,7 +12991,7 @@
       </c>
       <c r="BZ26" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="CA26" t="inlineStr">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
@@ -13021,12 +13021,12 @@
       </c>
       <c r="CF26" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -13036,7 +13036,7 @@
       </c>
       <c r="CI26" t="inlineStr">
         <is>
-          <t>16.51</t>
+          <t>16.57</t>
         </is>
       </c>
       <c r="CJ26" t="inlineStr">
@@ -13051,12 +13051,12 @@
       </c>
       <c r="CL26" t="inlineStr">
         <is>
-          <t>27.49</t>
+          <t>27.78</t>
         </is>
       </c>
       <c r="CM26" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5270</t>
         </is>
       </c>
       <c r="CN26" t="inlineStr">
@@ -13076,22 +13076,22 @@
       </c>
       <c r="CQ26" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CR26" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CS26" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CT26" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CU26" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>145.911</t>
+          <t>98.917</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -13138,7 +13138,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -13148,17 +13148,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-8.78</t>
+          <t>-11.03</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -13223,7 +13223,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-13.82</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -13248,7 +13248,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -13298,17 +13298,17 @@
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -13319,66 +13319,66 @@
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>266</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
+          <t>57.14</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr">
+        <is>
           <t>78.57</t>
         </is>
       </c>
-      <c r="AT27" t="inlineStr">
-        <is>
-          <t>67.22</t>
-        </is>
-      </c>
       <c r="AU27" t="n">
-        <v>0.83</v>
+        <v>0.15</v>
       </c>
       <c r="AV27" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>52.86</t>
+          <t>52.92</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>52.79</v>
+        <v>52.83</v>
       </c>
       <c r="BA27" t="n">
-        <v>54.74</v>
+        <v>54.65</v>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>57.19</t>
+          <t>57.08</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>35.24</t>
+          <t>35.55</t>
         </is>
       </c>
       <c r="BD27" t="n">
-        <v>-0.43</v>
+        <v>-0.39</v>
       </c>
       <c r="BE27" t="n">
-        <v>-0.66</v>
+        <v>-0.61</v>
       </c>
       <c r="BF27" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>-108.94</t>
+          <t>-108.21</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
@@ -13397,43 +13397,43 @@
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>321111602.0667614</t>
+          <t>320685940.6042553</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
         <is>
-          <t>7752629.0</t>
+          <t>5237706.0</t>
         </is>
       </c>
       <c r="BK27" t="n">
-        <v>10785672</v>
+        <v>9001865</v>
       </c>
       <c r="BL27" t="inlineStr">
         <is>
-          <t>11823210.0</t>
+          <t>10118227.0</t>
         </is>
       </c>
       <c r="BM27" t="n">
-        <v>25950292.18</v>
+        <v>24497841.7</v>
       </c>
       <c r="BN27" t="inlineStr">
         <is>
-          <t>-1037538</t>
+          <t>-1116362</t>
         </is>
       </c>
       <c r="BO27" t="inlineStr">
         <is>
-          <t>-1838753.197901726</t>
+          <t>-1840765.882135504</t>
         </is>
       </c>
       <c r="BP27" t="inlineStr">
         <is>
-          <t>-1580994.831872359</t>
+          <t>-1851835.645421285</t>
         </is>
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>7752629.0</t>
+          <t>5237706.0</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="BU27" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-9.25</t>
         </is>
       </c>
       <c r="BV27" t="inlineStr">
@@ -13478,7 +13478,7 @@
       </c>
       <c r="BZ27" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="CA27" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
@@ -13508,12 +13508,12 @@
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -13523,7 +13523,7 @@
       </c>
       <c r="CI27" t="inlineStr">
         <is>
-          <t>16.51</t>
+          <t>16.57</t>
         </is>
       </c>
       <c r="CJ27" t="inlineStr">
@@ -13538,12 +13538,12 @@
       </c>
       <c r="CL27" t="inlineStr">
         <is>
-          <t>27.49</t>
+          <t>27.78</t>
         </is>
       </c>
       <c r="CM27" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5270</t>
         </is>
       </c>
       <c r="CN27" t="inlineStr">
@@ -13563,12 +13563,12 @@
       </c>
       <c r="CQ27" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CR27" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CS27" t="inlineStr">
@@ -13578,7 +13578,7 @@
       </c>
       <c r="CT27" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CU27" t="inlineStr">
@@ -13600,7 +13600,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -13610,12 +13610,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>269.522</t>
+          <t>145.911</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -13625,7 +13625,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -13635,17 +13635,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-2.1</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-9.94</t>
+          <t>-8.78</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>-12.85</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -13735,7 +13735,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -13785,17 +13785,17 @@
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -13806,66 +13806,66 @@
       <c r="AP28" t="inlineStr"/>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>266</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>78.57</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>41.03</t>
+          <t>67.22</t>
         </is>
       </c>
       <c r="AU28" t="n">
-        <v>1.71</v>
+        <v>0.83</v>
       </c>
       <c r="AV28" t="n">
-        <v>-0.05</v>
+        <v>0.12</v>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>-3.9</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.86</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>52.72</v>
+        <v>52.79</v>
       </c>
       <c r="BA28" t="n">
-        <v>54.87</v>
+        <v>54.74</v>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>57.31</t>
+          <t>57.19</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>35.24</t>
         </is>
       </c>
       <c r="BD28" t="n">
-        <v>-0.5</v>
+        <v>-0.43</v>
       </c>
       <c r="BE28" t="n">
-        <v>-0.72</v>
+        <v>-0.66</v>
       </c>
       <c r="BF28" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>-109.73</t>
+          <t>-108.94</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
@@ -13884,43 +13884,43 @@
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>321111602.0667614</t>
+          <t>320685940.6042553</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr">
         <is>
-          <t>14393657.0</t>
+          <t>7752629.0</t>
         </is>
       </c>
       <c r="BK28" t="n">
-        <v>11871826.6</v>
+        <v>10785672</v>
       </c>
       <c r="BL28" t="inlineStr">
         <is>
-          <t>13182659.5</t>
+          <t>11823210.0</t>
         </is>
       </c>
       <c r="BM28" t="n">
-        <v>26927309.94</v>
+        <v>25950292.18</v>
       </c>
       <c r="BN28" t="inlineStr">
         <is>
-          <t>-1310832</t>
+          <t>-1037538</t>
         </is>
       </c>
       <c r="BO28" t="inlineStr">
         <is>
-          <t>-1885618.35536161</t>
+          <t>-1838753.197901726</t>
         </is>
       </c>
       <c r="BP28" t="inlineStr">
         <is>
-          <t>-1407071.31852131</t>
+          <t>-1580994.831872359</t>
         </is>
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>14393657.0</t>
+          <t>7752629.0</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="BU28" t="inlineStr">
         <is>
-          <t>-8.22</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="BV28" t="inlineStr">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="BZ28" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="CA28" t="inlineStr">
@@ -13985,7 +13985,7 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
@@ -13995,12 +13995,12 @@
       </c>
       <c r="CF28" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="CI28" t="inlineStr">
         <is>
-          <t>16.51</t>
+          <t>16.57</t>
         </is>
       </c>
       <c r="CJ28" t="inlineStr">
@@ -14025,12 +14025,12 @@
       </c>
       <c r="CL28" t="inlineStr">
         <is>
-          <t>27.49</t>
+          <t>27.78</t>
         </is>
       </c>
       <c r="CM28" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5270</t>
         </is>
       </c>
       <c r="CN28" t="inlineStr">
@@ -14050,22 +14050,22 @@
       </c>
       <c r="CQ28" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="CR28" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="CS28" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="CT28" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CU28" t="inlineStr">
